--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -1,34 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{21DB7C78-1483-EF49-82C2-A782A3870799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="288">
   <si>
     <t/>
   </si>
@@ -892,22 +875,19 @@
   </si>
   <si>
     <t>NRTHLND TOOL HELPER</t>
-  </si>
-  <si>
-    <t>TOY01D_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -928,16 +908,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1286,19 +1266,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F123"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9.953125" customWidth="1"/>
-    <col min="2" max="2" width="22.05859375" customWidth="1"/>
-    <col min="3" max="3" width="7.93359375" customWidth="1"/>
-    <col min="4" max="4" width="2.95703125" customWidth="1"/>
-    <col min="5" max="5" width="4.03515625" customWidth="1"/>
-    <col min="6" max="6" width="11.97265625" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1318,7 +1298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1338,7 +1318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1358,7 +1338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1378,7 +1358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1398,7 +1378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1418,7 +1398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1438,7 +1418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1458,7 +1438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -1478,7 +1458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1498,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1518,7 +1498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1538,7 +1518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1558,7 +1538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1578,7 +1558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -1598,7 +1578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1618,7 +1598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1638,7 +1618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
@@ -1658,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
@@ -1678,7 +1658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>55</v>
       </c>
@@ -1698,7 +1678,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
@@ -1718,7 +1698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>62</v>
       </c>
@@ -1738,7 +1718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>65</v>
       </c>
@@ -1758,7 +1738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>68</v>
       </c>
@@ -1778,7 +1758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>71</v>
       </c>
@@ -1798,7 +1778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>74</v>
       </c>
@@ -1818,7 +1798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>77</v>
       </c>
@@ -1838,7 +1818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>80</v>
       </c>
@@ -1858,7 +1838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>83</v>
       </c>
@@ -1878,7 +1858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>86</v>
       </c>
@@ -1898,7 +1878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>89</v>
       </c>
@@ -1918,7 +1898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>92</v>
       </c>
@@ -1938,7 +1918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>95</v>
       </c>
@@ -1958,7 +1938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>98</v>
       </c>
@@ -1978,7 +1958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
@@ -1998,7 +1978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>104</v>
       </c>
@@ -2018,7 +1998,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>108</v>
       </c>
@@ -2038,7 +2018,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>112</v>
       </c>
@@ -2058,7 +2038,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>115</v>
       </c>
@@ -2078,7 +2058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>118</v>
       </c>
@@ -2098,7 +2078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>121</v>
       </c>
@@ -2118,7 +2098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>124</v>
       </c>
@@ -2138,7 +2118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>127</v>
       </c>
@@ -2158,7 +2138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>129</v>
       </c>
@@ -2178,7 +2158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>131</v>
       </c>
@@ -2198,7 +2178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>133</v>
       </c>
@@ -2218,7 +2198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>135</v>
       </c>
@@ -2238,7 +2218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>137</v>
       </c>
@@ -2258,7 +2238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>139</v>
       </c>
@@ -2278,7 +2258,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>141</v>
       </c>
@@ -2298,7 +2278,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>143</v>
       </c>
@@ -2318,7 +2298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>145</v>
       </c>
@@ -2338,7 +2318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>147</v>
       </c>
@@ -2358,7 +2338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>149</v>
       </c>
@@ -2378,7 +2358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>151</v>
       </c>
@@ -2398,7 +2378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>153</v>
       </c>
@@ -2418,7 +2398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>155</v>
       </c>
@@ -2438,7 +2418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>157</v>
       </c>
@@ -2458,7 +2438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>159</v>
       </c>
@@ -2478,7 +2458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>161</v>
       </c>
@@ -2498,7 +2478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>163</v>
       </c>
@@ -2518,7 +2498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>165</v>
       </c>
@@ -2538,7 +2518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>167</v>
       </c>
@@ -2558,7 +2538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>169</v>
       </c>
@@ -2578,7 +2558,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>171</v>
       </c>
@@ -2598,7 +2578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>173</v>
       </c>
@@ -2618,7 +2598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>175</v>
       </c>
@@ -2638,7 +2618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>177</v>
       </c>
@@ -2658,7 +2638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>179</v>
       </c>
@@ -2678,7 +2658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>181</v>
       </c>
@@ -2698,7 +2678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>183</v>
       </c>
@@ -2718,7 +2698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>185</v>
       </c>
@@ -2738,7 +2718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>187</v>
       </c>
@@ -2758,7 +2738,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>189</v>
       </c>
@@ -2778,7 +2758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>191</v>
       </c>
@@ -2798,7 +2778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>193</v>
       </c>
@@ -2818,7 +2798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>195</v>
       </c>
@@ -2838,7 +2818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>197</v>
       </c>
@@ -2858,7 +2838,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>199</v>
       </c>
@@ -2878,7 +2858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>201</v>
       </c>
@@ -2898,7 +2878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>203</v>
       </c>
@@ -2918,7 +2898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>205</v>
       </c>
@@ -2938,7 +2918,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>207</v>
       </c>
@@ -2958,7 +2938,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>209</v>
       </c>
@@ -2978,7 +2958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>211</v>
       </c>
@@ -2998,27 +2978,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="1">
-        <v>20126490</v>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="D86" s="1">
-        <v>6</v>
-      </c>
-      <c r="E86" s="1">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>213</v>
       </c>
@@ -3038,7 +3018,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>215</v>
       </c>
@@ -3058,7 +3038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>217</v>
       </c>
@@ -3078,7 +3058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>219</v>
       </c>
@@ -3098,7 +3078,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>221</v>
       </c>
@@ -3118,7 +3098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>223</v>
       </c>
@@ -3138,7 +3118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>225</v>
       </c>
@@ -3158,7 +3138,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>227</v>
       </c>
@@ -3178,7 +3158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>229</v>
       </c>
@@ -3198,7 +3178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>231</v>
       </c>
@@ -3218,7 +3198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>233</v>
       </c>
@@ -3238,7 +3218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>235</v>
       </c>
@@ -3258,7 +3238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>237</v>
       </c>
@@ -3278,7 +3258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>239</v>
       </c>
@@ -3298,7 +3278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>241</v>
       </c>
@@ -3318,7 +3298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>243</v>
       </c>
@@ -3338,7 +3318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>245</v>
       </c>
@@ -3358,7 +3338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>247</v>
       </c>
@@ -3378,7 +3358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>249</v>
       </c>
@@ -3398,7 +3378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>251</v>
       </c>
@@ -3418,7 +3398,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>253</v>
       </c>
@@ -3438,7 +3418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>255</v>
       </c>
@@ -3458,7 +3438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>257</v>
       </c>
@@ -3478,7 +3458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>259</v>
       </c>
@@ -3498,7 +3478,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>261</v>
       </c>
@@ -3518,7 +3498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>263</v>
       </c>
@@ -3538,7 +3518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>265</v>
       </c>
@@ -3558,7 +3538,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>268</v>
       </c>
@@ -3578,7 +3558,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>270</v>
       </c>
@@ -3598,7 +3578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>272</v>
       </c>
@@ -3618,7 +3598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>274</v>
       </c>
@@ -3638,7 +3618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>276</v>
       </c>
@@ -3658,7 +3638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>278</v>
       </c>
@@ -3678,7 +3658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>280</v>
       </c>
@@ -3698,7 +3678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>282</v>
       </c>
@@ -3718,7 +3698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>284</v>
       </c>
@@ -3738,7 +3718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>286</v>
       </c>
@@ -3760,6 +3740,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -346,94 +346,94 @@
     <t>39</t>
   </si>
   <si>
+    <t>20135435</t>
+  </si>
+  <si>
+    <t>STMBL GY 3D MN FGURE</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20138254</t>
+  </si>
+  <si>
+    <t>JURASIC WORLD FIDGET</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>20140689</t>
+  </si>
+  <si>
+    <t>EMCO SD FLOWER MKR</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>20141254</t>
+  </si>
+  <si>
+    <t>SPNM  GABBYS DLHOUSE</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>20141255</t>
+  </si>
+  <si>
+    <t>BLOKEES TRANSFORMERS</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20092220</t>
+  </si>
+  <si>
+    <t>PLAY DOH VALUE SET</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135435</t>
-  </si>
-  <si>
-    <t>STMBL GY 3D MN FGURE</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20138254</t>
-  </si>
-  <si>
-    <t>JURASIC WORLD FIDGET</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>20140689</t>
-  </si>
-  <si>
-    <t>EMCO SD FLOWER MKR</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>20141254</t>
-  </si>
-  <si>
-    <t>SPNM  GABBYS DLHOUSE</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>20141255</t>
-  </si>
-  <si>
-    <t>BLOKEES TRANSFORMERS</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
-  </si>
-  <si>
-    <t>20092220</t>
-  </si>
-  <si>
-    <t>PLAY DOH VALUE SET</t>
-  </si>
-  <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
   </si>
   <si>
     <t>20140687</t>
@@ -2015,24 +2015,24 @@
         <v>110</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>107</v>
@@ -2040,19 +2040,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2060,19 +2060,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2080,19 +2080,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2100,19 +2100,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2255,7 +2255,7 @@
         <v>27</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,803 +11,767 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="258">
   <si>
     <t/>
   </si>
   <si>
+    <t>20140329</t>
+  </si>
+  <si>
+    <t>BLOKEES HERO INFINTY</t>
+  </si>
+  <si>
+    <t>TOY01D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20141255</t>
+  </si>
+  <si>
+    <t>BLOKEES TRANSFORMERS</t>
+  </si>
+  <si>
+    <t>20122578</t>
+  </si>
+  <si>
+    <t>CAT LITTLE MACHINES</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20102648</t>
+  </si>
+  <si>
+    <t>EMCO SLIME TIME</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20105569</t>
+  </si>
+  <si>
+    <t>EMCO DORAEMON MN FGR</t>
+  </si>
+  <si>
+    <t>20131699</t>
+  </si>
+  <si>
+    <t>EMCO PKEMON FACE OFF</t>
+  </si>
+  <si>
+    <t>20135483</t>
+  </si>
+  <si>
+    <t>EMCO VRTX ROPE LOOPR</t>
+  </si>
+  <si>
+    <t>20138689</t>
+  </si>
+  <si>
+    <t>EMCO INFINI-TWIST PY</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140689</t>
+  </si>
+  <si>
+    <t>EMCO SD FLOWER MKR</t>
+  </si>
+  <si>
+    <t>20053378</t>
+  </si>
+  <si>
+    <t>HELLO KITTY EGG 3345</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20102474</t>
+  </si>
+  <si>
+    <t>JRSC WORLD SNAP SQAD</t>
+  </si>
+  <si>
+    <t>20122574</t>
+  </si>
+  <si>
+    <t>H/W MONSTER TRUCK</t>
+  </si>
+  <si>
+    <t>20131019</t>
+  </si>
+  <si>
+    <t>JADA DISNEY FIGURE</t>
+  </si>
+  <si>
+    <t>20138254</t>
+  </si>
+  <si>
+    <t>JURASIC WORLD FIDGET</t>
+  </si>
+  <si>
+    <t>20131391</t>
+  </si>
+  <si>
+    <t>NRTHLND PLAYSET SERI</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20133201</t>
+  </si>
+  <si>
+    <t>NRTHLND BRICK SERIES</t>
+  </si>
+  <si>
+    <t>20133202</t>
+  </si>
+  <si>
+    <t>NRTHLND DIECAST SERI</t>
+  </si>
+  <si>
+    <t>20140760</t>
+  </si>
+  <si>
+    <t>NT PARKOUR CUTE PET</t>
+  </si>
+  <si>
+    <t>20052530</t>
+  </si>
+  <si>
+    <t>PLAY DOH MINI 4 PACK</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20134674</t>
+  </si>
+  <si>
+    <t>PLYDH ESSNTL CLR 10S</t>
+  </si>
+  <si>
+    <t>20135972</t>
+  </si>
+  <si>
+    <t>PLYDOH SNGLE CAN ASS</t>
+  </si>
+  <si>
+    <t>20138002</t>
+  </si>
+  <si>
+    <t>PIXAR IMPULSE  MINIS</t>
+  </si>
+  <si>
+    <t>20116479</t>
+  </si>
+  <si>
+    <t>SANRIO NECKLACE CHRT</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20127235</t>
+  </si>
+  <si>
+    <t>QMAN PKMON BRICK ASS</t>
+  </si>
+  <si>
+    <t>20132056</t>
+  </si>
+  <si>
+    <t>TROLLS BAND TGTHR FG</t>
+  </si>
+  <si>
+    <t>20132321</t>
+  </si>
+  <si>
+    <t>VR TOY BLN AIR JMB2S</t>
+  </si>
+  <si>
+    <t>20134962</t>
+  </si>
+  <si>
+    <t>RHINO MI GEMESH ASST</t>
+  </si>
+  <si>
+    <t>20135143</t>
+  </si>
+  <si>
+    <t>VR TOYS ALIEN SLIME</t>
+  </si>
+  <si>
+    <t>20135435</t>
+  </si>
+  <si>
+    <t>STMBL GY 3D MN FGURE</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20141254</t>
+  </si>
+  <si>
+    <t>SPNM  GABBYS DLHOUSE</t>
+  </si>
+  <si>
+    <t>20098313</t>
+  </si>
+  <si>
+    <t>WIKI IDM STORE BRICK</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20111543</t>
+  </si>
+  <si>
+    <t>WIKI IDM DLVRY TRUCK</t>
+  </si>
+  <si>
+    <t>20111544</t>
+  </si>
+  <si>
+    <t>WIKI I-MOBIL IDM TRK</t>
+  </si>
+  <si>
+    <t>20124279</t>
+  </si>
+  <si>
+    <t>WIKI BRI DLVRY VHCLE</t>
+  </si>
+  <si>
+    <t>20124280</t>
+  </si>
+  <si>
+    <t>WIKI DC IDM  DLVR TR</t>
+  </si>
+  <si>
+    <t>20124283</t>
+  </si>
+  <si>
+    <t>WIKI REMOTE CTRL ASS</t>
+  </si>
+  <si>
+    <t>20128423</t>
+  </si>
+  <si>
+    <t>WIKI VRBLE CMBNATION</t>
+  </si>
+  <si>
+    <t>20128425</t>
+  </si>
+  <si>
+    <t>WIKI DFRMTN RBOT ASS</t>
+  </si>
+  <si>
+    <t>20130556</t>
+  </si>
+  <si>
+    <t>WIKI BOYS SERIES</t>
+  </si>
+  <si>
+    <t>20132254</t>
+  </si>
+  <si>
+    <t>WIKI IDM UNFRM SRIES</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20092220</t>
+  </si>
+  <si>
+    <t>PLAY DOH VALUE SET</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
+  </si>
+  <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20133723</t>
+  </si>
+  <si>
+    <t>RHINO SWEET LICIOUS</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20109719</t>
+  </si>
+  <si>
+    <t>HW SHORT BLSTER 2021</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
     <t>20126490</t>
   </si>
   <si>
     <t>PRLY/PD BLND PCK AST</t>
   </si>
   <si>
-    <t>TOY01D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20053378</t>
-  </si>
-  <si>
-    <t>HELLO KITTY EGG 3345</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20105569</t>
-  </si>
-  <si>
-    <t>EMCO DORAEMON MN FGR</t>
-  </si>
-  <si>
-    <t>20131699</t>
-  </si>
-  <si>
-    <t>EMCO PKEMON FACE OFF</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20102648</t>
-  </si>
-  <si>
-    <t>EMCO SLIME TIME</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20111543</t>
-  </si>
-  <si>
-    <t>WIKI IDM DLVRY TRUCK</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20124279</t>
-  </si>
-  <si>
-    <t>WIKI BRI DLVRY VHCLE</t>
-  </si>
-  <si>
-    <t>20111544</t>
-  </si>
-  <si>
-    <t>WIKI I-MOBIL IDM TRK</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20098313</t>
-  </si>
-  <si>
-    <t>WIKI IDM STORE BRICK</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20135972</t>
-  </si>
-  <si>
-    <t>PLYDOH SNGLE CAN ASS</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20052530</t>
-  </si>
-  <si>
-    <t>PLAY DOH MINI 4 PACK</t>
+    <t>20138914</t>
+  </si>
+  <si>
+    <t>EMCO KIX BRIX</t>
+  </si>
+  <si>
+    <t>20135979</t>
+  </si>
+  <si>
+    <t>APOLO LTTLE BOTS ASS</t>
+  </si>
+  <si>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20136677</t>
+  </si>
+  <si>
+    <t>EMCO SANRIO CHARACTR</t>
+  </si>
+  <si>
+    <t>20139395</t>
+  </si>
+  <si>
+    <t>EMCO WASHY KITTIES</t>
+  </si>
+  <si>
+    <t>20080091</t>
+  </si>
+  <si>
+    <t>APOLO MSZ PULLBACK</t>
+  </si>
+  <si>
+    <t>20095864</t>
+  </si>
+  <si>
+    <t>WIKI D.CAST REAL CAR</t>
+  </si>
+  <si>
+    <t>20127783</t>
+  </si>
+  <si>
+    <t>APOLO HEAVY MACHNERY</t>
+  </si>
+  <si>
+    <t>20117276</t>
+  </si>
+  <si>
+    <t>HOT WHLS PULL BACK</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20140758</t>
+  </si>
+  <si>
+    <t>NT MY LOVELY PET</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20096159</t>
+  </si>
+  <si>
+    <t>EMCO POP A TOY</t>
+  </si>
+  <si>
+    <t>20129931</t>
+  </si>
+  <si>
+    <t>APOLO WOBBLE ASST</t>
+  </si>
+  <si>
+    <t>20133756</t>
+  </si>
+  <si>
+    <t>NORTH ARMY AIR FORCE</t>
+  </si>
+  <si>
+    <t>20140759</t>
+  </si>
+  <si>
+    <t>NT PUPPY PLAY SET</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>20133780</t>
+  </si>
+  <si>
+    <t>NRTHLND TOOL HELPER</t>
+  </si>
+  <si>
+    <t>20137553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
+  </si>
+  <si>
+    <t>20138913</t>
+  </si>
+  <si>
+    <t>EMCO POCKET TITANS</t>
+  </si>
+  <si>
+    <t>20140757</t>
+  </si>
+  <si>
+    <t>NT A.FG ESCHATOLOGY</t>
+  </si>
+  <si>
+    <t>20133771</t>
+  </si>
+  <si>
+    <t>NT HIP HOP BOY FGR</t>
+  </si>
+  <si>
+    <t>20133775</t>
+  </si>
+  <si>
+    <t>NORTH DIY ENGNE TRCK</t>
+  </si>
+  <si>
+    <t>20133786</t>
+  </si>
+  <si>
+    <t>NORTH POP UP FR/FROG</t>
+  </si>
+  <si>
+    <t>20140773</t>
+  </si>
+  <si>
+    <t>NT TOOL HOME ENGINR</t>
+  </si>
+  <si>
+    <t>20140756</t>
+  </si>
+  <si>
+    <t>NT SPACE STAR EXPLOR</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140768</t>
+  </si>
+  <si>
+    <t>NT TRAVEL PET HOME</t>
+  </si>
+  <si>
+    <t>20140769</t>
+  </si>
+  <si>
+    <t>NT PLBACK AEROPLANE</t>
+  </si>
+  <si>
+    <t>20140755</t>
+  </si>
+  <si>
+    <t>NT WAR OF TANKS WM</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20134962</t>
-  </si>
-  <si>
-    <t>RHINO MI GEMESH ASST</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20132254</t>
-  </si>
-  <si>
-    <t>WIKI IDM UNFRM SRIES</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20133201</t>
-  </si>
-  <si>
-    <t>NRTHLND BRICK SERIES</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20124283</t>
-  </si>
-  <si>
-    <t>WIKI REMOTE CTRL ASS</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20133202</t>
-  </si>
-  <si>
-    <t>NRTHLND DIECAST SERI</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20131391</t>
-  </si>
-  <si>
-    <t>NRTHLND PLAYSET SERI</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20130556</t>
-  </si>
-  <si>
-    <t>WIKI BOYS SERIES</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20140760</t>
-  </si>
-  <si>
-    <t>NT PARKOUR CUTE PET</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20116479</t>
-  </si>
-  <si>
-    <t>SANRIO NECKLACE CHRT</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20128425</t>
-  </si>
-  <si>
-    <t>WIKI DFRMTN RBOT ASS</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20128423</t>
-  </si>
-  <si>
-    <t>WIKI VRBLE CMBNATION</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20131019</t>
-  </si>
-  <si>
-    <t>JADA DISNEY FIGURE</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20102474</t>
-  </si>
-  <si>
-    <t>JRSC WORLD SNAP SQAD</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20132056</t>
-  </si>
-  <si>
-    <t>TROLLS BAND TGTHR FG</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20122578</t>
-  </si>
-  <si>
-    <t>CAT LITTLE MACHINES</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20135143</t>
-  </si>
-  <si>
-    <t>VR TOYS ALIEN SLIME</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20127235</t>
-  </si>
-  <si>
-    <t>QMAN PKMON BRICK ASS</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20122574</t>
-  </si>
-  <si>
-    <t>H/W MONSTER TRUCK</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20138002</t>
-  </si>
-  <si>
-    <t>PIXAR IMPULSE  MINIS</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20140329</t>
-  </si>
-  <si>
-    <t>BLOKEES HERO INFINTY</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20134674</t>
-  </si>
-  <si>
-    <t>PLYDH ESSNTL CLR 10S</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20132321</t>
-  </si>
-  <si>
-    <t>VR TOY BLN AIR JMB2S</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20124280</t>
-  </si>
-  <si>
-    <t>WIKI DC IDM  DLVR TR</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20135483</t>
-  </si>
-  <si>
-    <t>EMCO VRTX ROPE LOOPR</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20138689</t>
-  </si>
-  <si>
-    <t>EMCO INFINI-TWIST PY</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>20135435</t>
-  </si>
-  <si>
-    <t>STMBL GY 3D MN FGURE</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20138254</t>
-  </si>
-  <si>
-    <t>JURASIC WORLD FIDGET</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>20140689</t>
-  </si>
-  <si>
-    <t>EMCO SD FLOWER MKR</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>20141254</t>
-  </si>
-  <si>
-    <t>SPNM  GABBYS DLHOUSE</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>20141255</t>
-  </si>
-  <si>
-    <t>BLOKEES TRANSFORMERS</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
-  </si>
-  <si>
-    <t>20092220</t>
-  </si>
-  <si>
-    <t>PLAY DOH VALUE SET</t>
-  </si>
-  <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
-  </si>
-  <si>
-    <t>20133723</t>
-  </si>
-  <si>
-    <t>RHINO SWEET LICIOUS</t>
-  </si>
-  <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>20138914</t>
-  </si>
-  <si>
-    <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20135979</t>
-  </si>
-  <si>
-    <t>APOLO LTTLE BOTS ASS</t>
-  </si>
-  <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>20133756</t>
-  </si>
-  <si>
-    <t>NORTH ARMY AIR FORCE</t>
-  </si>
-  <si>
-    <t>20137553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
-  </si>
-  <si>
-    <t>20140758</t>
-  </si>
-  <si>
-    <t>NT MY LOVELY PET</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20127783</t>
-  </si>
-  <si>
-    <t>APOLO HEAVY MACHNERY</t>
-  </si>
-  <si>
-    <t>20136677</t>
-  </si>
-  <si>
-    <t>EMCO SANRIO CHARACTR</t>
-  </si>
-  <si>
-    <t>20140768</t>
-  </si>
-  <si>
-    <t>NT TRAVEL PET HOME</t>
-  </si>
-  <si>
-    <t>20095864</t>
-  </si>
-  <si>
-    <t>WIKI D.CAST REAL CAR</t>
-  </si>
-  <si>
-    <t>20129931</t>
-  </si>
-  <si>
-    <t>APOLO WOBBLE ASST</t>
-  </si>
-  <si>
-    <t>20133786</t>
-  </si>
-  <si>
-    <t>NORTH POP UP FR/FROG</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>20140755</t>
-  </si>
-  <si>
-    <t>NT WAR OF TANKS WM</t>
-  </si>
-  <si>
-    <t>20140773</t>
-  </si>
-  <si>
-    <t>NT TOOL HOME ENGINR</t>
-  </si>
-  <si>
-    <t>20133771</t>
-  </si>
-  <si>
-    <t>NT HIP HOP BOY FGR</t>
-  </si>
-  <si>
-    <t>20138913</t>
-  </si>
-  <si>
-    <t>EMCO POCKET TITANS</t>
-  </si>
-  <si>
-    <t>20139395</t>
-  </si>
-  <si>
-    <t>EMCO WASHY KITTIES</t>
-  </si>
-  <si>
-    <t>20140757</t>
-  </si>
-  <si>
-    <t>NT A.FG ESCHATOLOGY</t>
-  </si>
-  <si>
     <t>20141538</t>
   </si>
   <si>
@@ -821,60 +785,6 @@
   </si>
   <si>
     <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20096159</t>
-  </si>
-  <si>
-    <t>EMCO POP A TOY</t>
-  </si>
-  <si>
-    <t>20133775</t>
-  </si>
-  <si>
-    <t>NORTH DIY ENGNE TRCK</t>
-  </si>
-  <si>
-    <t>20140759</t>
-  </si>
-  <si>
-    <t>NT PUPPY PLAY SET</t>
-  </si>
-  <si>
-    <t>20140769</t>
-  </si>
-  <si>
-    <t>NT PLBACK AEROPLANE</t>
-  </si>
-  <si>
-    <t>20080091</t>
-  </si>
-  <si>
-    <t>APOLO MSZ PULLBACK</t>
-  </si>
-  <si>
-    <t>20140756</t>
-  </si>
-  <si>
-    <t>NT SPACE STAR EXPLOR</t>
-  </si>
-  <si>
-    <t>20117276</t>
-  </si>
-  <si>
-    <t>HOT WHLS PULL BACK</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20133780</t>
-  </si>
-  <si>
-    <t>NRTHLND TOOL HELPER</t>
   </si>
 </sst>
 </file>
@@ -1267,14 +1177,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1332,7 +1241,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -1340,19 +1249,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -1392,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -1400,11 +1309,11 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1412,7 +1321,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -1420,10 +1329,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1432,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -1440,30 +1349,30 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1472,7 +1381,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -1480,10 +1389,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1492,7 +1401,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1500,10 +1409,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1512,7 +1421,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1520,10 +1429,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1532,7 +1441,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1540,10 +1449,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1552,7 +1461,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1560,10 +1469,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1572,7 +1481,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1580,10 +1489,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1592,7 +1501,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1600,10 +1509,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1612,7 +1521,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1620,10 +1529,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1632,7 +1541,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1640,10 +1549,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1652,18 +1561,18 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1672,18 +1581,18 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1692,7 +1601,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1700,10 +1609,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1712,7 +1621,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1720,10 +1629,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1732,7 +1641,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1740,10 +1649,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1752,7 +1661,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1760,10 +1669,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1772,7 +1681,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1780,10 +1689,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1792,7 +1701,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1800,10 +1709,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1812,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1820,10 +1729,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1832,7 +1741,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1840,10 +1749,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1852,7 +1761,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1860,10 +1769,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1872,18 +1781,18 @@
         <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1892,7 +1801,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1900,10 +1809,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1912,7 +1821,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1920,10 +1829,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1932,7 +1841,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1940,10 +1849,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1952,7 +1861,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1960,10 +1869,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1972,7 +1881,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1980,10 +1889,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1992,18 +1901,18 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2012,18 +1921,18 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2032,18 +1941,18 @@
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2052,7 +1961,7 @@
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2060,10 +1969,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2072,7 +1981,7 @@
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2080,10 +1989,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2092,7 +2001,7 @@
         <v>4</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2100,19 +2009,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2120,16 +2029,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>4</v>
@@ -2140,19 +2049,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2160,19 +2069,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2180,19 +2089,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2200,19 +2109,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2220,70 +2129,70 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2292,7 +2201,7 @@
         <v>13</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2300,10 +2209,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2312,7 +2221,7 @@
         <v>13</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2320,10 +2229,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2332,7 +2241,7 @@
         <v>13</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2340,10 +2249,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2352,7 +2261,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2360,10 +2269,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2372,7 +2281,7 @@
         <v>13</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2380,10 +2289,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2392,7 +2301,7 @@
         <v>13</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2400,19 +2309,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2420,19 +2329,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2440,19 +2349,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2460,19 +2369,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2480,19 +2389,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2500,19 +2409,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2520,19 +2429,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2540,19 +2449,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2560,16 +2469,16 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>4</v>
@@ -2580,39 +2489,39 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2620,19 +2529,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2640,19 +2549,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2660,16 +2569,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>13</v>
@@ -2680,16 +2589,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>13</v>
@@ -2700,59 +2609,59 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2760,39 +2669,39 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2800,19 +2709,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2820,19 +2729,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2840,19 +2749,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2860,19 +2769,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2880,19 +2789,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2900,79 +2809,79 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2980,19 +2889,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3000,39 +2909,39 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3040,19 +2949,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3060,39 +2969,39 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3100,19 +3009,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3120,16 +3029,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>4</v>
@@ -3140,19 +3049,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3160,19 +3069,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3180,19 +3089,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3200,19 +3109,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3220,19 +3129,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3240,19 +3149,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3260,19 +3169,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3280,19 +3189,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3300,19 +3209,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3320,19 +3229,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3340,19 +3249,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3360,19 +3269,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3380,59 +3289,59 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3440,19 +3349,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3460,39 +3369,39 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3500,19 +3409,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3520,59 +3429,59 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>267</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>267</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3580,19 +3489,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3600,19 +3509,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3620,19 +3529,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3640,19 +3549,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3660,19 +3569,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>27</v>
+        <v>252</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3680,62 +3589,42 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>30</v>
+        <v>252</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>33</v>
+        <v>252</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -247,7 +247,7 @@
     <t>20111544</t>
   </si>
   <si>
-    <t>WIKI I-MOBIL IDM TRK</t>
+    <t>WIKI IDM TRK</t>
   </si>
   <si>
     <t>20124279</t>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="254">
   <si>
     <t/>
   </si>
@@ -37,6 +37,15 @@
     <t>BLOKEES TRANSFORMERS</t>
   </si>
   <si>
+    <t>20142150</t>
+  </si>
+  <si>
+    <t>BLOKEES BATMAN DV</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>20122578</t>
   </si>
   <si>
@@ -73,15 +82,6 @@
     <t>EMCO VRTX ROPE LOOPR</t>
   </si>
   <si>
-    <t>20138689</t>
-  </si>
-  <si>
-    <t>EMCO INFINI-TWIST PY</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20140689</t>
   </si>
   <si>
@@ -214,135 +214,129 @@
     <t>VR TOYS ALIEN SLIME</t>
   </si>
   <si>
-    <t>20135435</t>
-  </si>
-  <si>
-    <t>STMBL GY 3D MN FGURE</t>
+    <t>20141254</t>
+  </si>
+  <si>
+    <t>SPNM  GABBYS DLHOUSE</t>
+  </si>
+  <si>
+    <t>20098313</t>
+  </si>
+  <si>
+    <t>WIKI IDM STORE BRICK</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20111543</t>
+  </si>
+  <si>
+    <t>WIKI IDM DLVRY TRUCK</t>
+  </si>
+  <si>
+    <t>20111544</t>
+  </si>
+  <si>
+    <t>WIKI IDM TRK</t>
+  </si>
+  <si>
+    <t>20124279</t>
+  </si>
+  <si>
+    <t>WIKI BRI DLVRY VHCLE</t>
+  </si>
+  <si>
+    <t>20124280</t>
+  </si>
+  <si>
+    <t>WIKI DC IDM  DLVR TR</t>
+  </si>
+  <si>
+    <t>20124283</t>
+  </si>
+  <si>
+    <t>WIKI REMOTE CTRL ASS</t>
+  </si>
+  <si>
+    <t>20128423</t>
+  </si>
+  <si>
+    <t>WIKI VRBLE CMBNATION</t>
+  </si>
+  <si>
+    <t>20128425</t>
+  </si>
+  <si>
+    <t>WIKI DFRMTN RBOT ASS</t>
+  </si>
+  <si>
+    <t>20130556</t>
+  </si>
+  <si>
+    <t>WIKI BOYS SERIES</t>
+  </si>
+  <si>
+    <t>20132254</t>
+  </si>
+  <si>
+    <t>WIKI IDM UNFRM SRIES</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20092220</t>
+  </si>
+  <si>
+    <t>PLAY DOH VALUE SET</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
   </si>
   <si>
     <t>RT</t>
   </si>
   <si>
-    <t>20141254</t>
-  </si>
-  <si>
-    <t>SPNM  GABBYS DLHOUSE</t>
-  </si>
-  <si>
-    <t>20098313</t>
-  </si>
-  <si>
-    <t>WIKI IDM STORE BRICK</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20111543</t>
-  </si>
-  <si>
-    <t>WIKI IDM DLVRY TRUCK</t>
-  </si>
-  <si>
-    <t>20111544</t>
-  </si>
-  <si>
-    <t>WIKI IDM TRK</t>
-  </si>
-  <si>
-    <t>20124279</t>
-  </si>
-  <si>
-    <t>WIKI BRI DLVRY VHCLE</t>
-  </si>
-  <si>
-    <t>20124280</t>
-  </si>
-  <si>
-    <t>WIKI DC IDM  DLVR TR</t>
-  </si>
-  <si>
-    <t>20124283</t>
-  </si>
-  <si>
-    <t>WIKI REMOTE CTRL ASS</t>
-  </si>
-  <si>
-    <t>20128423</t>
-  </si>
-  <si>
-    <t>WIKI VRBLE CMBNATION</t>
-  </si>
-  <si>
-    <t>20128425</t>
-  </si>
-  <si>
-    <t>WIKI DFRMTN RBOT ASS</t>
-  </si>
-  <si>
-    <t>20130556</t>
-  </si>
-  <si>
-    <t>WIKI BOYS SERIES</t>
-  </si>
-  <si>
-    <t>20132254</t>
-  </si>
-  <si>
-    <t>WIKI IDM UNFRM SRIES</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
-  </si>
-  <si>
-    <t>20092220</t>
-  </si>
-  <si>
-    <t>PLAY DOH VALUE SET</t>
-  </si>
-  <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
     <t>20133852</t>
   </si>
   <si>
@@ -385,6 +379,12 @@
     <t xml:space="preserve">RHINO NAIL UNICORN  </t>
   </si>
   <si>
+    <t>20113158</t>
+  </si>
+  <si>
+    <t>EMCO ME&amp;MY CHARMZ</t>
+  </si>
+  <si>
     <t>20132776</t>
   </si>
   <si>
@@ -601,12 +601,6 @@
     <t>EMCO SANRIO CHARACTR</t>
   </si>
   <si>
-    <t>20139395</t>
-  </si>
-  <si>
-    <t>EMCO WASHY KITTIES</t>
-  </si>
-  <si>
     <t>20080091</t>
   </si>
   <si>
@@ -647,12 +641,6 @@
   </si>
   <si>
     <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20096159</t>
-  </si>
-  <si>
-    <t>EMCO POP A TOY</t>
   </si>
   <si>
     <t>20129931</t>
@@ -1177,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1261,10 +1249,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1301,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -1309,19 +1297,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -1329,10 +1317,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1341,7 +1329,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -1349,10 +1337,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1361,10 +1349,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1381,7 +1369,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -1564,7 +1552,7 @@
         <v>38</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,24 +1772,24 @@
         <v>56</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1821,7 +1809,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1829,11 +1817,11 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
@@ -1841,7 +1829,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1849,11 +1837,11 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
@@ -1861,7 +1849,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1869,11 +1857,11 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
@@ -1881,7 +1869,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1889,11 +1877,11 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
@@ -1901,7 +1889,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1909,11 +1897,11 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
@@ -1921,7 +1909,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1929,11 +1917,11 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
@@ -1941,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1949,11 +1937,11 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
@@ -1961,7 +1949,7 @@
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1969,11 +1957,11 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
@@ -1981,7 +1969,7 @@
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1989,19 +1977,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2009,16 +1997,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>4</v>
@@ -2029,19 +2017,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2049,19 +2037,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2069,19 +2057,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2089,19 +2077,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2109,22 +2097,22 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2138,10 +2126,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>107</v>
@@ -2158,13 +2146,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2178,10 +2166,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2198,10 +2186,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2218,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2238,10 +2226,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2258,10 +2246,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2278,10 +2266,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2298,10 +2286,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2341,7 +2329,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2361,7 +2349,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2504,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2521,7 +2509,7 @@
         <v>38</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2541,7 +2529,7 @@
         <v>38</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2561,7 +2549,7 @@
         <v>38</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2581,7 +2569,7 @@
         <v>38</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2601,7 +2589,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2621,10 +2609,10 @@
         <v>38</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2684,7 +2672,7 @@
         <v>27</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2864,7 +2852,7 @@
         <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2881,7 +2869,7 @@
         <v>47</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2901,7 +2889,7 @@
         <v>47</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -2924,7 +2912,7 @@
         <v>27</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,7 +2989,7 @@
         <v>47</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3041,7 +3029,7 @@
         <v>56</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3061,7 +3049,7 @@
         <v>56</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3081,7 +3069,7 @@
         <v>56</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3101,7 +3089,7 @@
         <v>56</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3121,7 +3109,7 @@
         <v>56</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3141,7 +3129,7 @@
         <v>56</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3161,7 +3149,7 @@
         <v>56</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3181,7 +3169,7 @@
         <v>56</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3241,7 +3229,7 @@
         <v>56</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3261,7 +3249,7 @@
         <v>56</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3284,7 +3272,7 @@
         <v>38</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3301,7 +3289,7 @@
         <v>56</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3321,10 +3309,10 @@
         <v>56</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3344,7 +3332,7 @@
         <v>47</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3381,10 +3369,10 @@
         <v>56</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3401,7 +3389,7 @@
         <v>56</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3461,7 +3449,7 @@
         <v>56</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3481,7 +3469,7 @@
         <v>56</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3501,7 +3489,7 @@
         <v>56</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3521,7 +3509,7 @@
         <v>56</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3541,7 +3529,7 @@
         <v>56</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3549,82 +3537,42 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -2898,7 +2898,7 @@
         <v>16</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2938,7 +2938,7 @@
         <v>38</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3078,7 +3078,7 @@
         <v>13</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3178,7 +3178,7 @@
         <v>27</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="263">
   <si>
     <t/>
   </si>
@@ -547,6 +547,30 @@
     <t>HW FAST&amp;FR2025 HNR88</t>
   </si>
   <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>20138915</t>
   </si>
   <si>
@@ -755,9 +779,6 @@
   </si>
   <si>
     <t>NT WAR OF TANKS WM</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
   <si>
     <t>20141538</t>
@@ -1171,13 +1192,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2852,10 +2874,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>10</v>
@@ -2872,41 +2894,41 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>16</v>
+        <v>185</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -2915,7 +2937,7 @@
         <v>47</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>10</v>
@@ -2923,10 +2945,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -2935,18 +2957,18 @@
         <v>47</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -2955,18 +2977,18 @@
         <v>47</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -2975,18 +2997,18 @@
         <v>47</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -2995,27 +3017,27 @@
         <v>47</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3023,19 +3045,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3043,19 +3065,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3063,10 +3085,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3075,18 +3097,18 @@
         <v>56</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3095,7 +3117,7 @@
         <v>56</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3103,10 +3125,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3115,7 +3137,7 @@
         <v>56</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3123,10 +3145,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3135,18 +3157,18 @@
         <v>56</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3163,10 +3185,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3175,18 +3197,18 @@
         <v>56</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3195,7 +3217,7 @@
         <v>56</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3203,10 +3225,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3215,7 +3237,7 @@
         <v>56</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3223,10 +3245,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3235,18 +3257,18 @@
         <v>56</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3255,7 +3277,7 @@
         <v>56</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3263,10 +3285,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3275,18 +3297,18 @@
         <v>56</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3295,7 +3317,7 @@
         <v>56</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3303,10 +3325,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3315,7 +3337,7 @@
         <v>56</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3323,10 +3345,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3335,18 +3357,18 @@
         <v>56</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3363,10 +3385,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3375,7 +3397,7 @@
         <v>56</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3383,10 +3405,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3395,18 +3417,18 @@
         <v>56</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3415,7 +3437,7 @@
         <v>56</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3423,10 +3445,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3443,10 +3465,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3455,7 +3477,7 @@
         <v>56</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3463,10 +3485,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3475,7 +3497,7 @@
         <v>56</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3483,10 +3505,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3495,7 +3517,7 @@
         <v>56</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3503,10 +3525,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3523,10 +3545,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3535,7 +3557,7 @@
         <v>56</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>248</v>
+        <v>71</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3543,10 +3565,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3555,10 +3577,10 @@
         <v>56</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>248</v>
+        <v>71</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3575,10 +3597,10 @@
         <v>56</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>248</v>
+        <v>71</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3595,9 +3617,69 @@
         <v>56</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="F121" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>104</v>
       </c>
     </row>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -76,12 +76,6 @@
     <t>EMCO PKEMON FACE OFF</t>
   </si>
   <si>
-    <t>20135483</t>
-  </si>
-  <si>
-    <t>EMCO VRTX ROPE LOOPR</t>
-  </si>
-  <si>
     <t>20140689</t>
   </si>
   <si>
@@ -800,6 +794,12 @@
   </si>
   <si>
     <t>TOYS/S SMALL STARS</t>
+  </si>
+  <si>
+    <t>20142227</t>
+  </si>
+  <si>
+    <t>EMCO POP A TOY NEW S</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1397,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -1405,19 +1405,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1437,7 +1437,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1477,7 +1477,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1497,7 +1497,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1505,19 +1505,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1537,7 +1537,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1557,10 +1557,10 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1577,27 +1577,27 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1617,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1637,7 +1637,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1657,7 +1657,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1677,7 +1677,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1697,7 +1697,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1717,7 +1717,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1737,7 +1737,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1757,7 +1757,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1777,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1797,7 +1797,7 @@
         <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1805,19 +1805,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1837,7 +1837,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1857,7 +1857,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1877,7 +1877,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1897,7 +1897,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1917,7 +1917,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1937,7 +1937,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1957,7 +1957,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1977,7 +1977,7 @@
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1994,10 +1994,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2037,7 +2037,7 @@
         <v>13</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2057,7 +2057,7 @@
         <v>13</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2077,7 +2077,7 @@
         <v>13</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2097,7 +2097,7 @@
         <v>13</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2117,18 +2117,18 @@
         <v>13</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2137,30 +2137,30 @@
         <v>13</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2177,7 +2177,7 @@
         <v>16</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2197,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2217,7 +2217,7 @@
         <v>16</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2237,7 +2237,7 @@
         <v>16</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2257,7 +2257,7 @@
         <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2277,7 +2277,7 @@
         <v>16</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2297,7 +2297,7 @@
         <v>16</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2314,10 +2314,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2334,10 +2334,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2354,10 +2354,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2374,10 +2374,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2394,10 +2394,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2414,10 +2414,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2434,10 +2434,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2454,10 +2454,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2474,7 +2474,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>4</v>
@@ -2494,13 +2494,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2514,13 +2514,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2534,7 +2534,7 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>13</v>
@@ -2554,7 +2554,7 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>13</v>
@@ -2574,10 +2574,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2594,7 +2594,7 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>16</v>
@@ -2614,13 +2614,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2634,13 +2634,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2654,10 +2654,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2674,13 +2674,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2694,13 +2694,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2714,10 +2714,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2734,10 +2734,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2754,10 +2754,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2774,10 +2774,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2794,10 +2794,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2814,10 +2814,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2834,10 +2834,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2854,13 +2854,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2874,10 +2874,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>10</v>
@@ -2885,19 +2885,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>10</v>
@@ -2905,19 +2905,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>185</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>10</v>
@@ -2934,13 +2934,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2954,13 +2954,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2974,13 +2974,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2994,13 +2994,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3014,13 +3014,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3034,10 +3034,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3054,10 +3054,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3074,10 +3074,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3094,10 +3094,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3114,7 +3114,7 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>13</v>
@@ -3134,13 +3134,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3154,13 +3154,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3174,7 +3174,7 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>16</v>
@@ -3194,7 +3194,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>16</v>
@@ -3214,7 +3214,7 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>16</v>
@@ -3234,13 +3234,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3254,13 +3254,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3274,10 +3274,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3294,10 +3294,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3314,10 +3314,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3334,13 +3334,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3354,13 +3354,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3374,10 +3374,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3394,13 +3394,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3414,13 +3414,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3434,10 +3434,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3454,10 +3454,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3474,10 +3474,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3494,10 +3494,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3514,10 +3514,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3534,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3554,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3574,10 +3574,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3594,10 +3594,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3614,33 +3614,33 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>256</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3654,13 +3654,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>258</v>
+        <v>102</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3674,13 +3674,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,24 +11,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="290">
   <si>
     <t/>
   </si>
   <si>
+    <t>20053378</t>
+  </si>
+  <si>
+    <t>HELLO KITTY EGG 3345</t>
+  </si>
+  <si>
+    <t>TOY01D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20131699</t>
+  </si>
+  <si>
+    <t>EMCO PKEMON FACE OFF</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20102648</t>
+  </si>
+  <si>
+    <t>EMCO SLIME TIME</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20135972</t>
+  </si>
+  <si>
+    <t>PLYDOH SNGLE CAN ASS</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20134962</t>
+  </si>
+  <si>
+    <t>RHINO MI GEMESH ASST</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>20140329</t>
   </si>
   <si>
     <t>BLOKEES HERO INFINTY</t>
   </si>
   <si>
-    <t>TOY01D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PT</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20052530</t>
+  </si>
+  <si>
+    <t>PLAY DOH MINI 4 PACK</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20111544</t>
+  </si>
+  <si>
+    <t>WIKI IDM TRK</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20098313</t>
+  </si>
+  <si>
+    <t>WIKI IDM STORE BRICK</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20133201</t>
+  </si>
+  <si>
+    <t>NRTHLND BRICK SERIES</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>20141255</t>
@@ -37,586 +118,691 @@
     <t>BLOKEES TRANSFORMERS</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20122578</t>
+  </si>
+  <si>
+    <t>CAT LITTLE MACHINES</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20105569</t>
+  </si>
+  <si>
+    <t>EMCO DORAEMON MN FGR</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20140689</t>
+  </si>
+  <si>
+    <t>EMCO SD FLOWER MKR</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20102474</t>
+  </si>
+  <si>
+    <t>JRSC WORLD SNAP SQAD</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20122574</t>
+  </si>
+  <si>
+    <t>H/W MONSTER TRUCK</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20131019</t>
+  </si>
+  <si>
+    <t>JADA DISNEY FIGURE</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20138254</t>
+  </si>
+  <si>
+    <t>JURASIC WORLD FIDGET</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20131391</t>
+  </si>
+  <si>
+    <t>NRTHLND PLAYSET SERI</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20133202</t>
+  </si>
+  <si>
+    <t>NRTHLND DIECAST SERI</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20140760</t>
+  </si>
+  <si>
+    <t>NT PARKOUR CUTE PET</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20134674</t>
+  </si>
+  <si>
+    <t>PLYDH ESSNTL CLR 10S</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20138002</t>
+  </si>
+  <si>
+    <t>PIXAR IMPULSE  MINIS</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20116479</t>
+  </si>
+  <si>
+    <t>SANRIO NECKLACE CHRT</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20127235</t>
+  </si>
+  <si>
+    <t>QMAN PKMON BRICK ASS</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20132056</t>
+  </si>
+  <si>
+    <t>TROLLS BAND TGTHR FG</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20132321</t>
+  </si>
+  <si>
+    <t>VR TOY BLN AIR JMB2S</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20135143</t>
+  </si>
+  <si>
+    <t>VR TOYS ALIEN SLIME</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20141254</t>
+  </si>
+  <si>
+    <t>SPNM  GABBYS DLHOUSE</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20111543</t>
+  </si>
+  <si>
+    <t>WIKI IDM DLVRY TRUCK</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20124279</t>
+  </si>
+  <si>
+    <t>WIKI BRI DLVRY VHCLE</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20124280</t>
+  </si>
+  <si>
+    <t>WIKI DC IDM  DLVR TR</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20124283</t>
+  </si>
+  <si>
+    <t>WIKI REMOTE CTRL ASS</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20128423</t>
+  </si>
+  <si>
+    <t>WIKI VRBLE CMBNATION</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20128425</t>
+  </si>
+  <si>
+    <t>WIKI DFRMTN RBOT ASS</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20130556</t>
+  </si>
+  <si>
+    <t>WIKI BOYS SERIES</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20132254</t>
+  </si>
+  <si>
+    <t>WIKI IDM UNFRM SRIES</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20092220</t>
+  </si>
+  <si>
+    <t>PLAY DOH VALUE SET</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20133723</t>
+  </si>
+  <si>
+    <t>RHINO SWEET LICIOUS</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20113158</t>
+  </si>
+  <si>
+    <t>EMCO ME&amp;MY CHARMZ</t>
+  </si>
+  <si>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20109719</t>
+  </si>
+  <si>
+    <t>HW SHORT BLSTER 2021</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20142036</t>
+  </si>
+  <si>
+    <t>TOYS/S SMALL STARS</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>20126490</t>
+  </si>
+  <si>
+    <t>PRLY/PD BLND PCK AST</t>
+  </si>
+  <si>
+    <t>20138914</t>
+  </si>
+  <si>
+    <t>EMCO KIX BRIX</t>
+  </si>
+  <si>
+    <t>20135979</t>
+  </si>
+  <si>
+    <t>APOLO LTTLE BOTS ASS</t>
+  </si>
+  <si>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
+    <t>20136677</t>
+  </si>
+  <si>
+    <t>EMCO SANRIO CHARACTR</t>
+  </si>
+  <si>
+    <t>20137553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
+  </si>
+  <si>
+    <t>20138913</t>
+  </si>
+  <si>
+    <t>EMCO POCKET TITANS</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
+  </si>
+  <si>
+    <t>20140768</t>
+  </si>
+  <si>
+    <t>NT TRAVEL PET HOME</t>
+  </si>
+  <si>
     <t>20142150</t>
   </si>
   <si>
     <t>BLOKEES BATMAN DV</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20122578</t>
-  </si>
-  <si>
-    <t>CAT LITTLE MACHINES</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20102648</t>
-  </si>
-  <si>
-    <t>EMCO SLIME TIME</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20105569</t>
-  </si>
-  <si>
-    <t>EMCO DORAEMON MN FGR</t>
-  </si>
-  <si>
-    <t>20131699</t>
-  </si>
-  <si>
-    <t>EMCO PKEMON FACE OFF</t>
-  </si>
-  <si>
-    <t>20140689</t>
-  </si>
-  <si>
-    <t>EMCO SD FLOWER MKR</t>
-  </si>
-  <si>
-    <t>20053378</t>
-  </si>
-  <si>
-    <t>HELLO KITTY EGG 3345</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20102474</t>
-  </si>
-  <si>
-    <t>JRSC WORLD SNAP SQAD</t>
-  </si>
-  <si>
-    <t>20122574</t>
-  </si>
-  <si>
-    <t>H/W MONSTER TRUCK</t>
-  </si>
-  <si>
-    <t>20131019</t>
-  </si>
-  <si>
-    <t>JADA DISNEY FIGURE</t>
-  </si>
-  <si>
-    <t>20138254</t>
-  </si>
-  <si>
-    <t>JURASIC WORLD FIDGET</t>
-  </si>
-  <si>
-    <t>20131391</t>
-  </si>
-  <si>
-    <t>NRTHLND PLAYSET SERI</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20133201</t>
-  </si>
-  <si>
-    <t>NRTHLND BRICK SERIES</t>
-  </si>
-  <si>
-    <t>20133202</t>
-  </si>
-  <si>
-    <t>NRTHLND DIECAST SERI</t>
-  </si>
-  <si>
-    <t>20140760</t>
-  </si>
-  <si>
-    <t>NT PARKOUR CUTE PET</t>
-  </si>
-  <si>
-    <t>20052530</t>
-  </si>
-  <si>
-    <t>PLAY DOH MINI 4 PACK</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20134674</t>
-  </si>
-  <si>
-    <t>PLYDH ESSNTL CLR 10S</t>
-  </si>
-  <si>
-    <t>20135972</t>
-  </si>
-  <si>
-    <t>PLYDOH SNGLE CAN ASS</t>
-  </si>
-  <si>
-    <t>20138002</t>
-  </si>
-  <si>
-    <t>PIXAR IMPULSE  MINIS</t>
-  </si>
-  <si>
-    <t>20116479</t>
-  </si>
-  <si>
-    <t>SANRIO NECKLACE CHRT</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20127235</t>
-  </si>
-  <si>
-    <t>QMAN PKMON BRICK ASS</t>
-  </si>
-  <si>
-    <t>20132056</t>
-  </si>
-  <si>
-    <t>TROLLS BAND TGTHR FG</t>
-  </si>
-  <si>
-    <t>20132321</t>
-  </si>
-  <si>
-    <t>VR TOY BLN AIR JMB2S</t>
-  </si>
-  <si>
-    <t>20134962</t>
-  </si>
-  <si>
-    <t>RHINO MI GEMESH ASST</t>
-  </si>
-  <si>
-    <t>20135143</t>
-  </si>
-  <si>
-    <t>VR TOYS ALIEN SLIME</t>
-  </si>
-  <si>
-    <t>20141254</t>
-  </si>
-  <si>
-    <t>SPNM  GABBYS DLHOUSE</t>
-  </si>
-  <si>
-    <t>20098313</t>
-  </si>
-  <si>
-    <t>WIKI IDM STORE BRICK</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20111543</t>
-  </si>
-  <si>
-    <t>WIKI IDM DLVRY TRUCK</t>
-  </si>
-  <si>
-    <t>20111544</t>
-  </si>
-  <si>
-    <t>WIKI IDM TRK</t>
-  </si>
-  <si>
-    <t>20124279</t>
-  </si>
-  <si>
-    <t>WIKI BRI DLVRY VHCLE</t>
-  </si>
-  <si>
-    <t>20124280</t>
-  </si>
-  <si>
-    <t>WIKI DC IDM  DLVR TR</t>
-  </si>
-  <si>
-    <t>20124283</t>
-  </si>
-  <si>
-    <t>WIKI REMOTE CTRL ASS</t>
-  </si>
-  <si>
-    <t>20128423</t>
-  </si>
-  <si>
-    <t>WIKI VRBLE CMBNATION</t>
-  </si>
-  <si>
-    <t>20128425</t>
-  </si>
-  <si>
-    <t>WIKI DFRMTN RBOT ASS</t>
-  </si>
-  <si>
-    <t>20130556</t>
-  </si>
-  <si>
-    <t>WIKI BOYS SERIES</t>
-  </si>
-  <si>
-    <t>20132254</t>
-  </si>
-  <si>
-    <t>WIKI IDM UNFRM SRIES</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
-  </si>
-  <si>
-    <t>20092220</t>
-  </si>
-  <si>
-    <t>PLAY DOH VALUE SET</t>
-  </si>
-  <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
-  </si>
-  <si>
-    <t>20133723</t>
-  </si>
-  <si>
-    <t>RHINO SWEET LICIOUS</t>
-  </si>
-  <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20113158</t>
-  </si>
-  <si>
-    <t>EMCO ME&amp;MY CHARMZ</t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>20126490</t>
-  </si>
-  <si>
-    <t>PRLY/PD BLND PCK AST</t>
-  </si>
-  <si>
-    <t>20138914</t>
-  </si>
-  <si>
-    <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20135979</t>
-  </si>
-  <si>
-    <t>APOLO LTTLE BOTS ASS</t>
-  </si>
-  <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20136677</t>
-  </si>
-  <si>
-    <t>EMCO SANRIO CHARACTR</t>
+    <t>20127783</t>
+  </si>
+  <si>
+    <t>APOLO HEAVY MACHNERY</t>
+  </si>
+  <si>
+    <t>20129931</t>
+  </si>
+  <si>
+    <t>APOLO WOBBLE ASST</t>
+  </si>
+  <si>
+    <t>20133780</t>
+  </si>
+  <si>
+    <t>NRTHLND TOOL HELPER</t>
+  </si>
+  <si>
+    <t>20117276</t>
+  </si>
+  <si>
+    <t>HOT WHLS PULL BACK</t>
+  </si>
+  <si>
+    <t>20095864</t>
+  </si>
+  <si>
+    <t>WIKI D.CAST REAL CAR</t>
+  </si>
+  <si>
+    <t>20133756</t>
+  </si>
+  <si>
+    <t>NORTH ARMY AIR FORCE</t>
   </si>
   <si>
     <t>20080091</t>
@@ -625,28 +811,16 @@
     <t>APOLO MSZ PULLBACK</t>
   </si>
   <si>
-    <t>20095864</t>
-  </si>
-  <si>
-    <t>WIKI D.CAST REAL CAR</t>
-  </si>
-  <si>
-    <t>20127783</t>
-  </si>
-  <si>
-    <t>APOLO HEAVY MACHNERY</t>
-  </si>
-  <si>
-    <t>20117276</t>
-  </si>
-  <si>
-    <t>HOT WHLS PULL BACK</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
+    <t>20140759</t>
+  </si>
+  <si>
+    <t>NT PUPPY PLAY SET</t>
+  </si>
+  <si>
+    <t>20142227</t>
+  </si>
+  <si>
+    <t>EMCO POP A TOY NEW S</t>
   </si>
   <si>
     <t>20140758</t>
@@ -655,66 +829,6 @@
     <t>NT MY LOVELY PET</t>
   </si>
   <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20129931</t>
-  </si>
-  <si>
-    <t>APOLO WOBBLE ASST</t>
-  </si>
-  <si>
-    <t>20133756</t>
-  </si>
-  <si>
-    <t>NORTH ARMY AIR FORCE</t>
-  </si>
-  <si>
-    <t>20140759</t>
-  </si>
-  <si>
-    <t>NT PUPPY PLAY SET</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>20133780</t>
-  </si>
-  <si>
-    <t>NRTHLND TOOL HELPER</t>
-  </si>
-  <si>
-    <t>20137553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
-  </si>
-  <si>
-    <t>20138913</t>
-  </si>
-  <si>
-    <t>EMCO POCKET TITANS</t>
-  </si>
-  <si>
     <t>20140757</t>
   </si>
   <si>
@@ -757,12 +871,6 @@
     <t>NT SPCL POLICE LIGHT</t>
   </si>
   <si>
-    <t>20140768</t>
-  </si>
-  <si>
-    <t>NT TRAVEL PET HOME</t>
-  </si>
-  <si>
     <t>20140769</t>
   </si>
   <si>
@@ -773,33 +881,6 @@
   </si>
   <si>
     <t>NT WAR OF TANKS WM</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20142036</t>
-  </si>
-  <si>
-    <t>TOYS/S SMALL STARS</t>
-  </si>
-  <si>
-    <t>20142227</t>
-  </si>
-  <si>
-    <t>EMCO POP A TOY NEW S</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1338,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -1265,10 +1346,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -1277,18 +1358,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -1297,7 +1378,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -1305,10 +1386,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -1317,7 +1398,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -1325,10 +1406,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -1337,7 +1418,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -1345,10 +1426,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1357,7 +1438,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>5</v>
@@ -1365,10 +1446,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1377,7 +1458,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -1385,10 +1466,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1397,7 +1478,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -1405,10 +1486,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1417,7 +1498,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1425,10 +1506,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1437,7 +1518,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1445,10 +1526,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1457,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1465,10 +1546,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1477,7 +1558,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1485,10 +1566,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1497,7 +1578,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1505,10 +1586,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1517,7 +1598,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1525,10 +1606,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1537,7 +1618,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1545,10 +1626,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1557,18 +1638,18 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1577,7 +1658,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1585,10 +1666,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1597,7 +1678,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1605,10 +1686,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1617,7 +1698,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1625,10 +1706,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1637,18 +1718,18 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1657,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1665,10 +1746,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1677,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1685,10 +1766,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1697,7 +1778,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1705,10 +1786,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1717,7 +1798,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1725,10 +1806,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1737,7 +1818,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1745,10 +1826,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1757,7 +1838,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1765,10 +1846,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1777,7 +1858,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1785,10 +1866,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1797,7 +1878,7 @@
         <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1805,10 +1886,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1817,7 +1898,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1825,10 +1906,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1837,7 +1918,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1845,10 +1926,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1857,7 +1938,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1865,10 +1946,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1877,7 +1958,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1885,10 +1966,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1897,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1905,10 +1986,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1917,7 +1998,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1925,10 +2006,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1937,7 +2018,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1945,10 +2026,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1957,7 +2038,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1965,19 +2046,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1985,19 +2066,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2005,19 +2086,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2025,19 +2106,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2045,19 +2126,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2065,19 +2146,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2085,79 +2166,79 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2165,19 +2246,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2185,19 +2266,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2205,19 +2286,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2225,19 +2306,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2245,19 +2326,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2265,19 +2346,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2285,19 +2366,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2305,19 +2386,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2325,19 +2406,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2345,19 +2426,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2365,19 +2446,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2385,19 +2466,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2405,19 +2486,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2425,19 +2506,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2445,19 +2526,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2465,79 +2546,79 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2545,39 +2626,39 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2585,19 +2666,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2605,59 +2686,59 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2665,39 +2746,39 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2705,19 +2786,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2725,19 +2806,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2745,19 +2826,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2765,19 +2846,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2785,19 +2866,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2805,19 +2886,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2825,19 +2906,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2845,179 +2926,179 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>183</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3025,19 +3106,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3045,36 +3126,36 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>4</v>
@@ -3085,19 +3166,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3105,59 +3186,59 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3165,39 +3246,39 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3205,19 +3286,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3225,39 +3306,39 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3265,19 +3346,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3285,79 +3366,79 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3365,19 +3446,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3385,39 +3466,39 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3425,19 +3506,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3445,19 +3526,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3465,39 +3546,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3505,19 +3586,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3525,19 +3606,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3545,19 +3626,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3565,19 +3646,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3585,19 +3666,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3605,82 +3686,82 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>256</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>256</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>183</v>
+        <v>59</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="286">
   <si>
     <t/>
   </si>
@@ -652,22 +652,10 @@
     <t>T&amp;F PLSTC ENGINE ASS</t>
   </si>
   <si>
-    <t>20126490</t>
-  </si>
-  <si>
-    <t>PRLY/PD BLND PCK AST</t>
-  </si>
-  <si>
     <t>20138914</t>
   </si>
   <si>
     <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20135979</t>
-  </si>
-  <si>
-    <t>APOLO LTTLE BOTS ASS</t>
   </si>
   <si>
     <t>20096148</t>
@@ -1273,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2581,7 +2569,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2761,7 +2749,7 @@
         <v>23</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3018,10 +3006,10 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3038,10 +3026,10 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3058,10 +3046,10 @@
         <v>20</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3078,7 +3066,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3098,10 +3086,10 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3115,10 +3103,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3135,13 +3123,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3161,15 +3149,15 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3178,18 +3166,18 @@
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3198,10 +3186,10 @@
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>233</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3221,7 +3209,7 @@
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>132</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3238,7 +3226,7 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3258,10 +3246,10 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>233</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3281,7 +3269,7 @@
         <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,7 +3286,7 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3318,10 +3306,10 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,7 +3329,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3358,10 +3346,10 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3378,10 +3366,10 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3401,7 +3389,7 @@
         <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3418,10 +3406,10 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3438,7 +3426,7 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3458,7 +3446,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3478,7 +3466,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3498,7 +3486,7 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3518,10 +3506,10 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3538,7 +3526,7 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3558,10 +3546,10 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3578,7 +3566,7 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3598,7 +3586,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3618,7 +3606,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3638,7 +3626,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3658,7 +3646,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3678,7 +3666,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3698,7 +3686,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3718,49 +3706,9 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F124" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="288">
   <si>
     <t/>
   </si>
@@ -638,6 +638,12 @@
   </si>
   <si>
     <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20142928</t>
+  </si>
+  <si>
+    <t>HW SILVER FF 2026</t>
   </si>
   <si>
     <t>20142036</t>
@@ -1261,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2963,13 +2969,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2986,10 +2992,10 @@
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3006,10 +3012,10 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3026,10 +3032,10 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3046,7 +3052,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3066,7 +3072,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3086,10 +3092,10 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,13 +3109,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3149,27 +3155,27 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>229</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3189,7 +3195,7 @@
         <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3209,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>229</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3226,10 +3232,10 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>231</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3269,7 +3275,7 @@
         <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3286,10 +3292,10 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3329,7 +3335,7 @@
         <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3346,10 +3352,10 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3389,7 +3395,7 @@
         <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3406,7 +3412,7 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3426,7 +3432,7 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3466,7 +3472,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3506,10 +3512,10 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3526,10 +3532,10 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3546,7 +3552,7 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3566,7 +3572,7 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3586,7 +3592,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3606,7 +3612,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3626,7 +3632,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3646,7 +3652,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3666,7 +3672,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3686,7 +3692,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3706,9 +3712,29 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F123" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="292">
   <si>
     <t/>
   </si>
@@ -356,6 +356,18 @@
   </si>
   <si>
     <t>37</t>
+  </si>
+  <si>
+    <t>20142945</t>
+  </si>
+  <si>
+    <t>EMCO METALZ PULLBACK</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>TG</t>
   </si>
   <si>
     <t>20134460</t>
@@ -1267,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2049,21 +2061,21 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2072,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2080,10 +2092,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2092,7 +2104,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2100,10 +2112,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2112,7 +2124,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2120,10 +2132,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2132,7 +2144,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2140,10 +2152,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2152,7 +2164,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2160,10 +2172,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2172,18 +2184,18 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2192,38 +2204,38 @@
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2232,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2240,10 +2252,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2252,7 +2264,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2260,10 +2272,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2272,7 +2284,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2280,10 +2292,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2292,7 +2304,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2300,10 +2312,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2312,7 +2324,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2320,10 +2332,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2332,7 +2344,7 @@
         <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2340,10 +2352,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2352,7 +2364,7 @@
         <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2360,19 +2372,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2380,10 +2392,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2392,7 +2404,7 @@
         <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2400,10 +2412,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2412,7 +2424,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2420,10 +2432,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2432,7 +2444,7 @@
         <v>14</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2440,10 +2452,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2452,7 +2464,7 @@
         <v>14</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2460,10 +2472,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2472,7 +2484,7 @@
         <v>14</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2480,10 +2492,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2492,7 +2504,7 @@
         <v>14</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2500,19 +2512,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2520,10 +2532,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2532,7 +2544,7 @@
         <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2540,10 +2552,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2555,15 +2567,15 @@
         <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2572,18 +2584,18 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2595,15 +2607,15 @@
         <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2612,18 +2624,18 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2635,15 +2647,15 @@
         <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2652,18 +2664,18 @@
         <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2680,10 +2692,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2692,7 +2704,7 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2700,10 +2712,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2715,15 +2727,15 @@
         <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2732,18 +2744,18 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2760,10 +2772,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2772,7 +2784,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2780,10 +2792,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2792,7 +2804,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2800,10 +2812,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2812,7 +2824,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2820,10 +2832,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2832,7 +2844,7 @@
         <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2840,10 +2852,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2852,7 +2864,7 @@
         <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2860,10 +2872,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2872,7 +2884,7 @@
         <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2880,10 +2892,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2892,7 +2904,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2900,10 +2912,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2912,7 +2924,7 @@
         <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2920,10 +2932,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2932,7 +2944,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2940,10 +2952,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2952,7 +2964,7 @@
         <v>17</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2960,10 +2972,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2972,7 +2984,7 @@
         <v>17</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2980,30 +2992,30 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3012,18 +3024,18 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3032,18 +3044,18 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3052,18 +3064,18 @@
         <v>20</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3072,7 +3084,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3080,10 +3092,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3092,7 +3104,7 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3100,10 +3112,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3112,38 +3124,38 @@
         <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3160,10 +3172,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3175,15 +3187,15 @@
         <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>231</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3192,18 +3204,18 @@
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3215,15 +3227,15 @@
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3235,15 +3247,15 @@
         <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>231</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3252,18 +3264,18 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3280,10 +3292,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3295,15 +3307,15 @@
         <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3312,18 +3324,18 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3340,10 +3352,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3355,15 +3367,15 @@
         <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3372,18 +3384,18 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3395,15 +3407,15 @@
         <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3415,15 +3427,15 @@
         <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3432,7 +3444,7 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3440,10 +3452,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3452,7 +3464,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3460,10 +3472,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3480,10 +3492,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3492,7 +3504,7 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3500,10 +3512,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3520,10 +3532,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3532,18 +3544,18 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3552,18 +3564,18 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3572,7 +3584,7 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3580,10 +3592,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3592,7 +3604,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3600,10 +3612,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3612,7 +3624,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3620,10 +3632,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3632,7 +3644,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3640,10 +3652,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3652,7 +3664,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3660,10 +3672,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3672,7 +3684,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3680,10 +3692,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3692,7 +3704,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3700,10 +3712,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3712,7 +3724,7 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3720,10 +3732,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3732,9 +3744,29 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F124" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -421,310 +421,310 @@
     <t>BARBIE JET TAG JNX28</t>
   </si>
   <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20133723</t>
+  </si>
+  <si>
+    <t>RHINO SWEET LICIOUS</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20113158</t>
+  </si>
+  <si>
+    <t>EMCO ME&amp;MY CHARMZ</t>
+  </si>
+  <si>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20109719</t>
+  </si>
+  <si>
+    <t>HW SHORT BLSTER 2021</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20142928</t>
+  </si>
+  <si>
+    <t>HW SILVER FF 2026</t>
+  </si>
+  <si>
+    <t>20142036</t>
+  </si>
+  <si>
+    <t>TOYS/S SMALL STARS</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>20138914</t>
+  </si>
+  <si>
+    <t>EMCO KIX BRIX</t>
+  </si>
+  <si>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
     <t>RT</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
-  </si>
-  <si>
-    <t>20133723</t>
-  </si>
-  <si>
-    <t>RHINO SWEET LICIOUS</t>
-  </si>
-  <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20113158</t>
-  </si>
-  <si>
-    <t>EMCO ME&amp;MY CHARMZ</t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20142928</t>
-  </si>
-  <si>
-    <t>HW SILVER FF 2026</t>
-  </si>
-  <si>
-    <t>20142036</t>
-  </si>
-  <si>
-    <t>TOYS/S SMALL STARS</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>20138914</t>
-  </si>
-  <si>
-    <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
   </si>
   <si>
     <t>20140777</t>
@@ -2227,15 +2227,15 @@
         <v>26</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2692,10 +2692,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2747,15 +2747,15 @@
         <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2952,10 +2952,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3027,15 +3027,15 @@
         <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3072,10 +3072,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3092,10 +3092,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3172,10 +3172,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3192,30 +3192,30 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3227,7 +3227,7 @@
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3267,7 +3267,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3407,7 +3407,7 @@
         <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3427,7 +3427,7 @@
         <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="291">
   <si>
     <t/>
   </si>
@@ -112,169 +112,766 @@
     <t>10</t>
   </si>
   <si>
+    <t>20105569</t>
+  </si>
+  <si>
+    <t>EMCO DORAEMON MN FGR</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20133202</t>
+  </si>
+  <si>
+    <t>NRTHLND DIECAST SERI</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20122578</t>
+  </si>
+  <si>
+    <t>CAT LITTLE MACHINES</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20111543</t>
+  </si>
+  <si>
+    <t>WIKI IDM DLVRY TRUCK</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20124279</t>
+  </si>
+  <si>
+    <t>WIKI BRI DLVRY VHCLE</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20124280</t>
+  </si>
+  <si>
+    <t>WIKI DC IDM  DLVR TR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20124283</t>
+  </si>
+  <si>
+    <t>WIKI REMOTE CTRL ASS</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20122574</t>
+  </si>
+  <si>
+    <t>H/W MONSTER TRUCK</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20138254</t>
+  </si>
+  <si>
+    <t>JURASIC WORLD FIDGET</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20102474</t>
+  </si>
+  <si>
+    <t>JRSC WORLD SNAP SQAD</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20135143</t>
+  </si>
+  <si>
+    <t>VR TOYS ALIEN SLIME</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20128425</t>
+  </si>
+  <si>
+    <t>WIKI DFRMTN RBOT ASS</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20130556</t>
+  </si>
+  <si>
+    <t>WIKI BOYS SERIES</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20131019</t>
+  </si>
+  <si>
+    <t>JADA DISNEY FIGURE</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20132254</t>
+  </si>
+  <si>
+    <t>WIKI IDM UNFRM SRIES</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20140760</t>
+  </si>
+  <si>
+    <t>NT PARKOUR CUTE PET</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20127235</t>
+  </si>
+  <si>
+    <t>QMAN PKMON BRICK ASS</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20134674</t>
+  </si>
+  <si>
+    <t>PLYDH ESSNTL CLR 10S</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20138002</t>
+  </si>
+  <si>
+    <t>PIXAR IMPULSE  MINIS</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20132056</t>
+  </si>
+  <si>
+    <t>TROLLS BAND TGTHR FG</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20128423</t>
+  </si>
+  <si>
+    <t>WIKI VRBLE CMBNATION</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20113158</t>
+  </si>
+  <si>
+    <t>EMCO ME&amp;MY CHARMZ</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20140689</t>
+  </si>
+  <si>
+    <t>EMCO SD FLOWER MKR</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20132321</t>
+  </si>
+  <si>
+    <t>VR TOY BLN AIR JMB2S</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20116479</t>
+  </si>
+  <si>
+    <t>SANRIO NECKLACE CHRT</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20131391</t>
+  </si>
+  <si>
+    <t>NRTHLND PLAYSET SERI</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20142945</t>
+  </si>
+  <si>
+    <t>EMCO METALZ PULLBACK</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20092220</t>
+  </si>
+  <si>
+    <t>PLAY DOH VALUE SET</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
+  </si>
+  <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20133723</t>
+  </si>
+  <si>
+    <t>RHINO SWEET LICIOUS</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20142928</t>
+  </si>
+  <si>
+    <t>HW SILVER FF 2026</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20109719</t>
+  </si>
+  <si>
+    <t>HW SHORT BLSTER 2021</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20142036</t>
+  </si>
+  <si>
+    <t>TOYS/S SMALL STARS</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>20138914</t>
+  </si>
+  <si>
+    <t>EMCO KIX BRIX</t>
+  </si>
+  <si>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
+    <t>20136677</t>
+  </si>
+  <si>
+    <t>EMCO SANRIO CHARACTR</t>
+  </si>
+  <si>
+    <t>20140768</t>
+  </si>
+  <si>
+    <t>NT TRAVEL PET HOME</t>
+  </si>
+  <si>
+    <t>20127783</t>
+  </si>
+  <si>
+    <t>APOLO HEAVY MACHNERY</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20117276</t>
+  </si>
+  <si>
+    <t>HOT WHLS PULL BACK</t>
+  </si>
+  <si>
+    <t>20095864</t>
+  </si>
+  <si>
+    <t>WIKI D.CAST REAL CAR</t>
+  </si>
+  <si>
+    <t>20080091</t>
+  </si>
+  <si>
+    <t>APOLO MSZ PULLBACK</t>
+  </si>
+  <si>
+    <t>20142227</t>
+  </si>
+  <si>
+    <t>EMCO POP A TOY NEW S</t>
+  </si>
+  <si>
+    <t>20140758</t>
+  </si>
+  <si>
+    <t>NT MY LOVELY PET</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20137553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
+  </si>
+  <si>
+    <t>20142150</t>
+  </si>
+  <si>
+    <t>BLOKEES BATMAN DV</t>
+  </si>
+  <si>
+    <t>20129931</t>
+  </si>
+  <si>
+    <t>APOLO WOBBLE ASST</t>
+  </si>
+  <si>
+    <t>20133756</t>
+  </si>
+  <si>
+    <t>NORTH ARMY AIR FORCE</t>
+  </si>
+  <si>
+    <t>20140759</t>
+  </si>
+  <si>
+    <t>NT PUPPY PLAY SET</t>
+  </si>
+  <si>
+    <t>20140757</t>
+  </si>
+  <si>
+    <t>NT A.FG ESCHATOLOGY</t>
+  </si>
+  <si>
+    <t>20133771</t>
+  </si>
+  <si>
+    <t>NT HIP HOP BOY FGR</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>20138913</t>
+  </si>
+  <si>
+    <t>EMCO POCKET TITANS</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
+  </si>
+  <si>
+    <t>20133780</t>
+  </si>
+  <si>
+    <t>NRTHLND TOOL HELPER</t>
+  </si>
+  <si>
     <t>20141255</t>
   </si>
   <si>
     <t>BLOKEES TRANSFORMERS</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20122578</t>
-  </si>
-  <si>
-    <t>CAT LITTLE MACHINES</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20105569</t>
-  </si>
-  <si>
-    <t>EMCO DORAEMON MN FGR</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20140689</t>
-  </si>
-  <si>
-    <t>EMCO SD FLOWER MKR</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20102474</t>
-  </si>
-  <si>
-    <t>JRSC WORLD SNAP SQAD</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20122574</t>
-  </si>
-  <si>
-    <t>H/W MONSTER TRUCK</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20131019</t>
-  </si>
-  <si>
-    <t>JADA DISNEY FIGURE</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20138254</t>
-  </si>
-  <si>
-    <t>JURASIC WORLD FIDGET</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20131391</t>
-  </si>
-  <si>
-    <t>NRTHLND PLAYSET SERI</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20133202</t>
-  </si>
-  <si>
-    <t>NRTHLND DIECAST SERI</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20140760</t>
-  </si>
-  <si>
-    <t>NT PARKOUR CUTE PET</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20134674</t>
-  </si>
-  <si>
-    <t>PLYDH ESSNTL CLR 10S</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20138002</t>
-  </si>
-  <si>
-    <t>PIXAR IMPULSE  MINIS</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20116479</t>
-  </si>
-  <si>
-    <t>SANRIO NECKLACE CHRT</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20127235</t>
-  </si>
-  <si>
-    <t>QMAN PKMON BRICK ASS</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20132056</t>
-  </si>
-  <si>
-    <t>TROLLS BAND TGTHR FG</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20132321</t>
-  </si>
-  <si>
-    <t>VR TOY BLN AIR JMB2S</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20135143</t>
-  </si>
-  <si>
-    <t>VR TOYS ALIEN SLIME</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>20140773</t>
+  </si>
+  <si>
+    <t>NT TOOL HOME ENGINR</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140756</t>
+  </si>
+  <si>
+    <t>NT SPACE STAR EXPLOR</t>
+  </si>
+  <si>
+    <t>20140769</t>
+  </si>
+  <si>
+    <t>NT PLBACK AEROPLANE</t>
+  </si>
+  <si>
+    <t>20133775</t>
+  </si>
+  <si>
+    <t>NORTH DIY ENGNE TRCK</t>
+  </si>
+  <si>
+    <t>20140755</t>
+  </si>
+  <si>
+    <t>NT WAR OF TANKS WM</t>
   </si>
   <si>
     <t>20141254</t>
@@ -283,610 +880,10 @@
     <t>SPNM  GABBYS DLHOUSE</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20111543</t>
-  </si>
-  <si>
-    <t>WIKI IDM DLVRY TRUCK</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20124279</t>
-  </si>
-  <si>
-    <t>WIKI BRI DLVRY VHCLE</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20124280</t>
-  </si>
-  <si>
-    <t>WIKI DC IDM  DLVR TR</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20124283</t>
-  </si>
-  <si>
-    <t>WIKI REMOTE CTRL ASS</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20128423</t>
-  </si>
-  <si>
-    <t>WIKI VRBLE CMBNATION</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20128425</t>
-  </si>
-  <si>
-    <t>WIKI DFRMTN RBOT ASS</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20130556</t>
-  </si>
-  <si>
-    <t>WIKI BOYS SERIES</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20132254</t>
-  </si>
-  <si>
-    <t>WIKI IDM UNFRM SRIES</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20142945</t>
-  </si>
-  <si>
-    <t>EMCO METALZ PULLBACK</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>TG</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
-  </si>
-  <si>
-    <t>20092220</t>
-  </si>
-  <si>
-    <t>PLAY DOH VALUE SET</t>
-  </si>
-  <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
-  </si>
-  <si>
-    <t>20133723</t>
-  </si>
-  <si>
-    <t>RHINO SWEET LICIOUS</t>
-  </si>
-  <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20113158</t>
-  </si>
-  <si>
-    <t>EMCO ME&amp;MY CHARMZ</t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20142928</t>
-  </si>
-  <si>
-    <t>HW SILVER FF 2026</t>
-  </si>
-  <si>
-    <t>20142036</t>
-  </si>
-  <si>
-    <t>TOYS/S SMALL STARS</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>20138914</t>
-  </si>
-  <si>
-    <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20136677</t>
-  </si>
-  <si>
-    <t>EMCO SANRIO CHARACTR</t>
-  </si>
-  <si>
-    <t>20137553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
-  </si>
-  <si>
-    <t>20138913</t>
-  </si>
-  <si>
-    <t>EMCO POCKET TITANS</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>20140768</t>
-  </si>
-  <si>
-    <t>NT TRAVEL PET HOME</t>
-  </si>
-  <si>
-    <t>20142150</t>
-  </si>
-  <si>
-    <t>BLOKEES BATMAN DV</t>
-  </si>
-  <si>
-    <t>20127783</t>
-  </si>
-  <si>
-    <t>APOLO HEAVY MACHNERY</t>
-  </si>
-  <si>
-    <t>20129931</t>
-  </si>
-  <si>
-    <t>APOLO WOBBLE ASST</t>
-  </si>
-  <si>
-    <t>20133780</t>
-  </si>
-  <si>
-    <t>NRTHLND TOOL HELPER</t>
-  </si>
-  <si>
-    <t>20117276</t>
-  </si>
-  <si>
-    <t>HOT WHLS PULL BACK</t>
-  </si>
-  <si>
-    <t>20095864</t>
-  </si>
-  <si>
-    <t>WIKI D.CAST REAL CAR</t>
-  </si>
-  <si>
-    <t>20133756</t>
-  </si>
-  <si>
-    <t>NORTH ARMY AIR FORCE</t>
-  </si>
-  <si>
-    <t>20080091</t>
-  </si>
-  <si>
-    <t>APOLO MSZ PULLBACK</t>
-  </si>
-  <si>
-    <t>20140759</t>
-  </si>
-  <si>
-    <t>NT PUPPY PLAY SET</t>
-  </si>
-  <si>
-    <t>20142227</t>
-  </si>
-  <si>
-    <t>EMCO POP A TOY NEW S</t>
-  </si>
-  <si>
-    <t>20140758</t>
-  </si>
-  <si>
-    <t>NT MY LOVELY PET</t>
-  </si>
-  <si>
-    <t>20140757</t>
-  </si>
-  <si>
-    <t>NT A.FG ESCHATOLOGY</t>
-  </si>
-  <si>
-    <t>20133771</t>
-  </si>
-  <si>
-    <t>NT HIP HOP BOY FGR</t>
-  </si>
-  <si>
-    <t>20133775</t>
-  </si>
-  <si>
-    <t>NORTH DIY ENGNE TRCK</t>
-  </si>
-  <si>
     <t>20133786</t>
   </si>
   <si>
     <t>NORTH POP UP FR/FROG</t>
-  </si>
-  <si>
-    <t>20140773</t>
-  </si>
-  <si>
-    <t>NT TOOL HOME ENGINR</t>
-  </si>
-  <si>
-    <t>20140756</t>
-  </si>
-  <si>
-    <t>NT SPACE STAR EXPLOR</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20140769</t>
-  </si>
-  <si>
-    <t>NT PLBACK AEROPLANE</t>
-  </si>
-  <si>
-    <t>20140755</t>
-  </si>
-  <si>
-    <t>NT WAR OF TANKS WM</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1727,24 +1724,24 @@
         <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1752,19 +1749,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1772,19 +1769,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1792,19 +1789,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1812,22 +1809,22 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2047,35 +2044,35 @@
         <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2084,7 +2081,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2092,10 +2089,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2104,7 +2101,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2112,10 +2109,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2124,7 +2121,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2132,10 +2129,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2144,7 +2141,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2152,10 +2149,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2164,10 +2161,10 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2201,30 +2198,30 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2232,10 +2229,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2244,7 +2241,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2252,10 +2249,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2264,7 +2261,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2272,10 +2269,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2284,7 +2281,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2292,10 +2289,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2304,7 +2301,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2312,10 +2309,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2324,7 +2321,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2332,19 +2329,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2352,19 +2349,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2372,19 +2369,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2392,10 +2389,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2404,7 +2401,7 @@
         <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2412,10 +2409,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2424,7 +2421,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2432,10 +2429,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2444,7 +2441,7 @@
         <v>14</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2452,10 +2449,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2464,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2472,10 +2469,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2484,7 +2481,7 @@
         <v>14</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2492,10 +2489,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2504,7 +2501,7 @@
         <v>14</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2512,10 +2509,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2524,7 +2521,7 @@
         <v>14</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2532,10 +2529,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2552,10 +2549,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2572,10 +2569,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2584,18 +2581,18 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2604,7 +2601,7 @@
         <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2612,10 +2609,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2624,18 +2621,18 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2644,7 +2641,7 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2652,10 +2649,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2664,18 +2661,18 @@
         <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2684,18 +2681,18 @@
         <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2704,18 +2701,18 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2724,7 +2721,7 @@
         <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2732,10 +2729,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2744,18 +2741,18 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2764,7 +2761,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2772,10 +2769,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2784,7 +2781,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2792,10 +2789,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2804,7 +2801,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2812,10 +2809,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2824,7 +2821,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2832,10 +2829,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2844,7 +2841,7 @@
         <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2852,10 +2849,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2864,7 +2861,7 @@
         <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2872,10 +2869,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2884,7 +2881,7 @@
         <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2892,10 +2889,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2904,7 +2901,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2912,10 +2909,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2924,7 +2921,7 @@
         <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2932,10 +2929,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2944,7 +2941,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2952,10 +2949,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2964,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2972,10 +2969,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2984,7 +2981,7 @@
         <v>17</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2992,30 +2989,30 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3024,18 +3021,18 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3044,18 +3041,18 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3067,15 +3064,15 @@
         <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3084,7 +3081,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3092,10 +3089,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3104,7 +3101,7 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3112,10 +3109,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3124,7 +3121,7 @@
         <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3132,10 +3129,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3144,18 +3141,18 @@
         <v>20</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3167,15 +3164,15 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3184,18 +3181,18 @@
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3204,18 +3201,18 @@
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3224,18 +3221,18 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>237</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3244,18 +3241,18 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3264,18 +3261,18 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3284,7 +3281,7 @@
         <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3292,10 +3289,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3304,7 +3301,7 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3312,10 +3309,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3324,18 +3321,18 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3344,7 +3341,7 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3352,10 +3349,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3364,7 +3361,7 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3372,10 +3369,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3384,18 +3381,18 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3404,18 +3401,18 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>237</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3424,18 +3421,18 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>237</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3444,18 +3441,18 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3464,7 +3461,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3472,10 +3469,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3484,7 +3481,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3492,10 +3489,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3504,7 +3501,7 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3512,10 +3509,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3524,7 +3521,7 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3532,10 +3529,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3544,7 +3541,7 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3552,10 +3549,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3564,18 +3561,18 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>66</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3584,18 +3581,18 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3604,7 +3601,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3612,10 +3609,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3624,7 +3621,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3632,10 +3629,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3644,7 +3641,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3652,10 +3649,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3664,7 +3661,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3672,10 +3669,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3684,7 +3681,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3692,10 +3689,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3704,7 +3701,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3712,10 +3709,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3724,7 +3721,7 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3732,10 +3729,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3744,7 +3741,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3752,21 +3749,61 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F124" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="293">
   <si>
     <t/>
   </si>
@@ -361,28 +361,427 @@
     <t>TG</t>
   </si>
   <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
+  </si>
+  <si>
+    <t>20143374</t>
+  </si>
+  <si>
+    <t>BARBIE SILICON POUCH</t>
+  </si>
+  <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20133723</t>
+  </si>
+  <si>
+    <t>RHINO SWEET LICIOUS</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20141254</t>
+  </si>
+  <si>
+    <t>SPNM  GABBYS DLHOUSE</t>
+  </si>
+  <si>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20142928</t>
+  </si>
+  <si>
+    <t>HW SILVER FF 2026</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20109719</t>
+  </si>
+  <si>
+    <t>HW SHORT BLSTER 2021</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20142036</t>
+  </si>
+  <si>
+    <t>TOYS/S SMALL STARS</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>20138914</t>
+  </si>
+  <si>
+    <t>EMCO KIX BRIX</t>
+  </si>
+  <si>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20140755</t>
+  </si>
+  <si>
+    <t>NT WAR OF TANKS WM</t>
+  </si>
+  <si>
+    <t>20140773</t>
+  </si>
+  <si>
+    <t>NT TOOL HOME ENGINR</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
     <t>20134460</t>
   </si>
   <si>
     <t>MEGA PKEMON POKEBALL</t>
   </si>
   <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
+    <t>20133786</t>
+  </si>
+  <si>
+    <t>NORTH POP UP FR/FROG</t>
+  </si>
+  <si>
+    <t>20136677</t>
+  </si>
+  <si>
+    <t>EMCO SANRIO CHARACTR</t>
+  </si>
+  <si>
+    <t>20137553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
+  </si>
+  <si>
+    <t>20138913</t>
+  </si>
+  <si>
+    <t>EMCO POCKET TITANS</t>
+  </si>
+  <si>
+    <t>20140756</t>
+  </si>
+  <si>
+    <t>NT SPACE STAR EXPLOR</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
   </si>
   <si>
     <t>20092220</t>
@@ -391,331 +790,46 @@
     <t>PLAY DOH VALUE SET</t>
   </si>
   <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
-  </si>
-  <si>
-    <t>20133723</t>
-  </si>
-  <si>
-    <t>RHINO SWEET LICIOUS</t>
-  </si>
-  <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20142928</t>
-  </si>
-  <si>
-    <t>HW SILVER FF 2026</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20142036</t>
-  </si>
-  <si>
-    <t>TOYS/S SMALL STARS</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
-  </si>
-  <si>
-    <t>20138914</t>
-  </si>
-  <si>
-    <t>EMCO KIX BRIX</t>
-  </si>
-  <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20136677</t>
-  </si>
-  <si>
-    <t>EMCO SANRIO CHARACTR</t>
-  </si>
-  <si>
     <t>20140768</t>
   </si>
   <si>
     <t>NT TRAVEL PET HOME</t>
   </si>
   <si>
+    <t>20140769</t>
+  </si>
+  <si>
+    <t>NT PLBACK AEROPLANE</t>
+  </si>
+  <si>
+    <t>20142150</t>
+  </si>
+  <si>
+    <t>BLOKEES BATMAN DV</t>
+  </si>
+  <si>
     <t>20127783</t>
   </si>
   <si>
     <t>APOLO HEAVY MACHNERY</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>20129931</t>
+  </si>
+  <si>
+    <t>APOLO WOBBLE ASST</t>
+  </si>
+  <si>
+    <t>20133775</t>
+  </si>
+  <si>
+    <t>NORTH DIY ENGNE TRCK</t>
+  </si>
+  <si>
+    <t>20133780</t>
+  </si>
+  <si>
+    <t>NRTHLND TOOL HELPER</t>
   </si>
   <si>
     <t>20117276</t>
@@ -724,18 +838,48 @@
     <t>HOT WHLS PULL BACK</t>
   </si>
   <si>
+    <t>20133756</t>
+  </si>
+  <si>
+    <t>NORTH ARMY AIR FORCE</t>
+  </si>
+  <si>
+    <t>20141255</t>
+  </si>
+  <si>
+    <t>BLOKEES TRANSFORMERS</t>
+  </si>
+  <si>
     <t>20095864</t>
   </si>
   <si>
     <t>WIKI D.CAST REAL CAR</t>
   </si>
   <si>
+    <t>20140759</t>
+  </si>
+  <si>
+    <t>NT PUPPY PLAY SET</t>
+  </si>
+  <si>
     <t>20080091</t>
   </si>
   <si>
     <t>APOLO MSZ PULLBACK</t>
   </si>
   <si>
+    <t>20140757</t>
+  </si>
+  <si>
+    <t>NT A.FG ESCHATOLOGY</t>
+  </si>
+  <si>
+    <t>20133771</t>
+  </si>
+  <si>
+    <t>NT HIP HOP BOY FGR</t>
+  </si>
+  <si>
     <t>20142227</t>
   </si>
   <si>
@@ -746,144 +890,6 @@
   </si>
   <si>
     <t>NT MY LOVELY PET</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20137553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
-  </si>
-  <si>
-    <t>20142150</t>
-  </si>
-  <si>
-    <t>BLOKEES BATMAN DV</t>
-  </si>
-  <si>
-    <t>20129931</t>
-  </si>
-  <si>
-    <t>APOLO WOBBLE ASST</t>
-  </si>
-  <si>
-    <t>20133756</t>
-  </si>
-  <si>
-    <t>NORTH ARMY AIR FORCE</t>
-  </si>
-  <si>
-    <t>20140759</t>
-  </si>
-  <si>
-    <t>NT PUPPY PLAY SET</t>
-  </si>
-  <si>
-    <t>20140757</t>
-  </si>
-  <si>
-    <t>NT A.FG ESCHATOLOGY</t>
-  </si>
-  <si>
-    <t>20133771</t>
-  </si>
-  <si>
-    <t>NT HIP HOP BOY FGR</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>20138913</t>
-  </si>
-  <si>
-    <t>EMCO POCKET TITANS</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>20133780</t>
-  </si>
-  <si>
-    <t>NRTHLND TOOL HELPER</t>
-  </si>
-  <si>
-    <t>20141255</t>
-  </si>
-  <si>
-    <t>BLOKEES TRANSFORMERS</t>
-  </si>
-  <si>
-    <t>20140773</t>
-  </si>
-  <si>
-    <t>NT TOOL HOME ENGINR</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20140756</t>
-  </si>
-  <si>
-    <t>NT SPACE STAR EXPLOR</t>
-  </si>
-  <si>
-    <t>20140769</t>
-  </si>
-  <si>
-    <t>NT PLBACK AEROPLANE</t>
-  </si>
-  <si>
-    <t>20133775</t>
-  </si>
-  <si>
-    <t>NORTH DIY ENGNE TRCK</t>
-  </si>
-  <si>
-    <t>20140755</t>
-  </si>
-  <si>
-    <t>NT WAR OF TANKS WM</t>
-  </si>
-  <si>
-    <t>20141254</t>
-  </si>
-  <si>
-    <t>SPNM  GABBYS DLHOUSE</t>
-  </si>
-  <si>
-    <t>20133786</t>
-  </si>
-  <si>
-    <t>NORTH POP UP FR/FROG</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2061,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2081,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2101,7 +2107,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2121,18 +2127,18 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2141,7 +2147,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2149,10 +2155,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2161,10 +2167,10 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2178,10 +2184,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2201,7 +2207,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2221,7 +2227,7 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2241,7 +2247,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2261,7 +2267,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2281,7 +2287,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2301,7 +2307,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2321,7 +2327,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2701,7 +2707,7 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>81</v>
@@ -2709,10 +2715,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2721,18 +2727,18 @@
         <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2741,18 +2747,18 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2761,7 +2767,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2769,10 +2775,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2781,7 +2787,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2789,10 +2795,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2801,7 +2807,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2809,10 +2815,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2821,7 +2827,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2829,10 +2835,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2841,7 +2847,7 @@
         <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2849,10 +2855,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2861,7 +2867,7 @@
         <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2869,10 +2875,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2881,7 +2887,7 @@
         <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2889,10 +2895,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2901,7 +2907,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2909,10 +2915,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2921,7 +2927,7 @@
         <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2929,10 +2935,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2941,7 +2947,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2949,39 +2955,39 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -2989,10 +2995,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3001,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>81</v>
@@ -3009,10 +3015,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3021,7 +3027,7 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3029,10 +3035,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3041,18 +3047,18 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3061,7 +3067,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3069,10 +3075,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3081,7 +3087,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3089,10 +3095,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3101,27 +3107,27 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3129,30 +3135,30 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3164,15 +3170,15 @@
         <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>225</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3181,18 +3187,18 @@
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>225</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3201,18 +3207,18 @@
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3221,7 +3227,7 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3229,10 +3235,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3241,18 +3247,18 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3261,7 +3267,7 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3269,10 +3275,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3281,7 +3287,7 @@
         <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3289,10 +3295,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3301,18 +3307,18 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3321,18 +3327,18 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3341,7 +3347,7 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3349,10 +3355,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3361,7 +3367,7 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3369,10 +3375,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3381,18 +3387,18 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3401,7 +3407,7 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3409,10 +3415,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3421,18 +3427,18 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3441,18 +3447,18 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3461,7 +3467,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3469,10 +3475,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3481,7 +3487,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3489,10 +3495,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3501,18 +3507,18 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3521,18 +3527,18 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3541,18 +3547,18 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>238</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3561,18 +3567,18 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3581,18 +3587,18 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3601,7 +3607,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3609,10 +3615,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3621,7 +3627,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3629,10 +3635,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3641,7 +3647,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3649,10 +3655,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3661,7 +3667,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3669,10 +3675,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3681,7 +3687,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3689,10 +3695,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3701,7 +3707,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3709,10 +3715,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3721,7 +3727,7 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3729,10 +3735,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3741,7 +3747,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3749,10 +3755,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -3761,18 +3767,18 @@
         <v>23</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -3781,29 +3787,9 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F126" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="296">
   <si>
     <t/>
   </si>
@@ -715,45 +715,45 @@
     <t>RT,(E-24B)</t>
   </si>
   <si>
+    <t>20133786</t>
+  </si>
+  <si>
+    <t>NORTH POP UP FR/FROG</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
     <t>20134460</t>
   </si>
   <si>
     <t>MEGA PKEMON POKEBALL</t>
   </si>
   <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20133786</t>
-  </si>
-  <si>
-    <t>NORTH POP UP FR/FROG</t>
-  </si>
-  <si>
     <t>20136677</t>
   </si>
   <si>
@@ -830,6 +830,15 @@
   </si>
   <si>
     <t>NRTHLND TOOL HELPER</t>
+  </si>
+  <si>
+    <t>20143747</t>
+  </si>
+  <si>
+    <t>EMCO MYSTERY DMPLG</t>
+  </si>
+  <si>
+    <t>PT,(E-45B)</t>
   </si>
   <si>
     <t>20117276</t>
@@ -1282,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2067,7 +2076,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2087,7 +2096,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2107,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2127,7 +2136,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>124</v>
@@ -2147,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2167,7 +2176,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>124</v>
@@ -3607,18 +3616,18 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3635,10 +3644,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3655,10 +3664,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3667,7 +3676,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3675,10 +3684,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3695,10 +3704,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3707,7 +3716,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3715,10 +3724,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3735,10 +3744,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3747,7 +3756,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3755,10 +3764,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -3770,15 +3779,15 @@
         <v>29</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -3787,9 +3796,29 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F126" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="299">
   <si>
     <t/>
   </si>
@@ -400,6 +400,15 @@
     <t>BARBIE SILICON POUCH</t>
   </si>
   <si>
+    <t>20143910</t>
+  </si>
+  <si>
+    <t>BARBIE CUTIE KYCHAIN</t>
+  </si>
+  <si>
+    <t>PT,(E-74B)</t>
+  </si>
+  <si>
     <t>20133852</t>
   </si>
   <si>
@@ -448,12 +457,24 @@
     <t>SPNM  GABBYS DLHOUSE</t>
   </si>
   <si>
+    <t>20130066</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS ASS</t>
+  </si>
+  <si>
     <t>20132776</t>
   </si>
   <si>
     <t>HW CMPACT CASE HYJ70</t>
   </si>
   <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
     <t>20124309</t>
   </si>
   <si>
@@ -490,18 +511,6 @@
     <t>RKC ROLL SPD METAL</t>
   </si>
   <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
     <t>20137630</t>
   </si>
   <si>
@@ -514,78 +523,78 @@
     <t>HOT WHEELS MBL BASIC</t>
   </si>
   <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
     <t>20142928</t>
   </si>
   <si>
     <t>HW SILVER FF 2026</t>
   </si>
   <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
     <t>20140691</t>
   </si>
   <si>
     <t>HW 58TH ANNIV HDH54</t>
   </si>
   <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
     <t>20140693</t>
   </si>
   <si>
     <t>HW FAST&amp;F 25TH ANNIV</t>
   </si>
   <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
     <t>20137359</t>
   </si>
   <si>
     <t>HW NEON SPEED HLH72</t>
   </si>
   <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
     <t>20140695</t>
   </si>
   <si>
     <t>HW PANTONE JKY47</t>
   </si>
   <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
     <t>20140694</t>
   </si>
   <si>
     <t>HW THE HOT ONES</t>
   </si>
   <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
     <t>20094698</t>
   </si>
   <si>
@@ -688,31 +697,31 @@
     <t>EMCO PAT MYSTERY BOX</t>
   </si>
   <si>
+    <t>20140755</t>
+  </si>
+  <si>
+    <t>NT WAR OF TANKS WM</t>
+  </si>
+  <si>
+    <t>20140773</t>
+  </si>
+  <si>
+    <t>NT TOOL HOME ENGINR</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
     <t>20133041</t>
   </si>
   <si>
     <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20140755</t>
-  </si>
-  <si>
-    <t>NT WAR OF TANKS WM</t>
-  </si>
-  <si>
-    <t>20140773</t>
-  </si>
-  <si>
-    <t>NT TOOL HOME ENGINR</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
   </si>
   <si>
     <t>20133786</t>
@@ -1291,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2193,21 +2202,21 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2216,7 +2225,7 @@
         <v>11</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2224,10 +2233,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2236,7 +2245,7 @@
         <v>11</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2244,10 +2253,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2256,7 +2265,7 @@
         <v>11</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2264,10 +2273,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2276,7 +2285,7 @@
         <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2284,10 +2293,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2296,7 +2305,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2304,10 +2313,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2316,7 +2325,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2324,10 +2333,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2336,7 +2345,7 @@
         <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2344,19 +2353,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2364,10 +2373,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2376,7 +2385,7 @@
         <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2384,10 +2393,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2396,7 +2405,7 @@
         <v>14</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2404,10 +2413,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2416,7 +2425,7 @@
         <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2424,10 +2433,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2436,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2444,10 +2453,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2456,7 +2465,7 @@
         <v>14</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2464,10 +2473,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2476,7 +2485,7 @@
         <v>14</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2484,10 +2493,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2496,7 +2505,7 @@
         <v>14</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2504,10 +2513,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2516,7 +2525,7 @@
         <v>14</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2524,10 +2533,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2536,7 +2545,7 @@
         <v>14</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2544,19 +2553,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2564,10 +2573,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2576,7 +2585,7 @@
         <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2584,10 +2593,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2596,18 +2605,18 @@
         <v>17</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2616,7 +2625,7 @@
         <v>17</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2624,10 +2633,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2636,18 +2645,18 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2656,7 +2665,7 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -2664,10 +2673,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2676,18 +2685,18 @@
         <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2696,18 +2705,18 @@
         <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2716,18 +2725,18 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2736,18 +2745,18 @@
         <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2756,7 +2765,7 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2764,10 +2773,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2776,7 +2785,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2784,10 +2793,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2796,7 +2805,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2804,10 +2813,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2816,7 +2825,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2824,10 +2833,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2836,7 +2845,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2844,10 +2853,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2856,7 +2865,7 @@
         <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2864,10 +2873,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2876,7 +2885,7 @@
         <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2884,10 +2893,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2896,7 +2905,7 @@
         <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2904,10 +2913,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2916,7 +2925,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2924,10 +2933,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2936,7 +2945,7 @@
         <v>17</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2944,10 +2953,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2956,7 +2965,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2964,30 +2973,30 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -2996,18 +3005,18 @@
         <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3016,18 +3025,18 @@
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3036,18 +3045,18 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3056,7 +3065,7 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3064,10 +3073,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3076,7 +3085,7 @@
         <v>20</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3084,10 +3093,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3096,7 +3105,7 @@
         <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3104,10 +3113,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3116,38 +3125,38 @@
         <v>20</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3164,10 +3173,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3184,10 +3193,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3204,10 +3213,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3219,15 +3228,15 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3244,10 +3253,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3256,10 +3265,10 @@
         <v>23</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>238</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3276,18 +3285,18 @@
         <v>23</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>241</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3296,7 +3305,7 @@
         <v>23</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3304,10 +3313,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3316,18 +3325,18 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>233</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3339,15 +3348,15 @@
         <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3356,7 +3365,7 @@
         <v>23</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3364,10 +3373,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3376,7 +3385,7 @@
         <v>23</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3384,10 +3393,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3396,18 +3405,18 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3416,18 +3425,18 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3444,10 +3453,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3456,7 +3465,7 @@
         <v>23</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3464,10 +3473,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3476,7 +3485,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3484,10 +3493,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3496,7 +3505,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3504,10 +3513,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3516,18 +3525,18 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3539,15 +3548,15 @@
         <v>17</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>238</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3556,18 +3565,18 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3576,18 +3585,18 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3596,7 +3605,7 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3604,10 +3613,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3616,10 +3625,10 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>275</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3639,15 +3648,15 @@
         <v>20</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3656,7 +3665,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3664,10 +3673,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3676,7 +3685,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3684,10 +3693,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3704,10 +3713,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3716,7 +3725,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3724,10 +3733,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3744,10 +3753,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3756,7 +3765,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3764,10 +3773,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -3784,10 +3793,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -3796,18 +3805,18 @@
         <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -3819,6 +3828,26 @@
         <v>32</v>
       </c>
       <c r="F126" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>5</v>
       </c>
     </row>
